--- a/Book2.xlsx
+++ b/Book2.xlsx
@@ -1,17 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\retainer_mtc1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ravi24op/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCDA745C-FF4F-40DF-AA8D-23DC3FEEF5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0104A6-0238-314D-AFCA-DE0795E07498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26760" windowHeight="15585" activeTab="2" xr2:uid="{71229555-CA1D-43C0-A936-3A264D92DD28}"/>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77ACD4C1-1F1A-410C-98BA-E575D10B3DB0}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" activeTab="2" xr2:uid="{71229555-CA1D-43C0-A936-3A264D92DD28}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 25-MAY-2026 )" sheetId="3" r:id="rId1"/>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="136">
   <si>
     <t>Daily Production Report : 25-MAY-2026</t>
   </si>
@@ -508,7 +507,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -653,6 +652,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -718,24 +723,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -749,21 +744,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -820,9 +800,6 @@
     <xf numFmtId="164" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -830,9 +807,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -865,9 +839,6 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -895,9 +866,6 @@
     <xf numFmtId="0" fontId="2" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -919,9 +887,6 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="21" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -929,12 +894,59 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="24" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="23" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="25" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2221,5706 +2233,5758 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A4:AG76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" customWidth="1"/>
-    <col min="3" max="15" width="12.28515625" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" customWidth="1"/>
-    <col min="19" max="31" width="12.28515625" customWidth="1"/>
-    <col min="32" max="33" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="3" max="15" width="12.33203125" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" customWidth="1"/>
+    <col min="18" max="18" width="12.6640625" customWidth="1"/>
+    <col min="19" max="31" width="12.33203125" customWidth="1"/>
+    <col min="32" max="33" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A4" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
     </row>
-    <row r="5" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="14" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14" t="s">
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="Q5" s="15" t="s">
+      <c r="Q5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="R5" s="16" t="s">
+      <c r="R5" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="S5" s="17" t="s">
+      <c r="S5" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="T5" s="17"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="17"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="17"/>
-      <c r="AB5" s="17"/>
-      <c r="AC5" s="17"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="17"/>
-      <c r="AF5" s="17" t="s">
+      <c r="T5" s="71"/>
+      <c r="U5" s="71"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="71"/>
+      <c r="X5" s="71"/>
+      <c r="Y5" s="71"/>
+      <c r="Z5" s="71"/>
+      <c r="AA5" s="71"/>
+      <c r="AB5" s="71"/>
+      <c r="AC5" s="71"/>
+      <c r="AD5" s="71"/>
+      <c r="AE5" s="71"/>
+      <c r="AF5" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="AG5" s="18" t="s">
+      <c r="AG5" s="72" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="20" t="s">
+      <c r="B6" s="68"/>
+      <c r="C6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="J6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="20" t="s">
+      <c r="M6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="20" t="s">
+      <c r="N6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="O6" s="20" t="s">
+      <c r="O6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="15" t="s">
+      <c r="P6" s="75"/>
+      <c r="Q6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="R6" s="16"/>
-      <c r="S6" s="21" t="s">
+      <c r="R6" s="76"/>
+      <c r="S6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="T6" s="21" t="s">
+      <c r="T6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="U6" s="21" t="s">
+      <c r="U6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="V6" s="21" t="s">
+      <c r="V6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="W6" s="21" t="s">
+      <c r="W6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="X6" s="21" t="s">
+      <c r="X6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="Y6" s="21" t="s">
+      <c r="Y6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="Z6" s="21" t="s">
+      <c r="Z6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="AA6" s="21" t="s">
+      <c r="AA6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="AB6" s="21" t="s">
+      <c r="AB6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="AC6" s="21" t="s">
+      <c r="AC6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="AD6" s="21" t="s">
+      <c r="AD6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE6" s="21" t="s">
+      <c r="AE6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AF6" s="17"/>
-      <c r="AG6" s="18"/>
+      <c r="AF6" s="71"/>
+      <c r="AG6" s="72"/>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A7" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="23">
+      <c r="B7" s="68"/>
+      <c r="C7" s="14">
         <v>2.9249999999999998</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="14">
         <v>27</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="14">
         <v>0.23200000000000001</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="14">
         <v>70</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="14">
         <v>50</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="14">
         <v>100</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="14">
         <v>20</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="14">
         <v>26</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="14">
         <v>25</v>
       </c>
-      <c r="L7" s="23">
+      <c r="L7" s="14">
         <v>24.125</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="14">
         <v>4</v>
       </c>
-      <c r="N7" s="23">
+      <c r="N7" s="14">
         <v>11</v>
       </c>
-      <c r="O7" s="23">
+      <c r="O7" s="14">
         <v>40</v>
       </c>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="24">
+      <c r="P7" s="14"/>
+      <c r="Q7" s="15">
         <v>45</v>
       </c>
-      <c r="R7" s="24"/>
-      <c r="S7" s="25">
+      <c r="R7" s="15"/>
+      <c r="S7" s="16">
         <v>2.9249999999999998</v>
       </c>
-      <c r="T7" s="25">
+      <c r="T7" s="16">
         <v>27</v>
       </c>
-      <c r="U7" s="25">
+      <c r="U7" s="16">
         <v>0.23200000000000001</v>
       </c>
-      <c r="V7" s="25">
+      <c r="V7" s="16">
         <v>70</v>
       </c>
-      <c r="W7" s="25">
+      <c r="W7" s="16">
         <v>50</v>
       </c>
-      <c r="X7" s="25">
+      <c r="X7" s="16">
         <v>17</v>
       </c>
-      <c r="Y7" s="25">
+      <c r="Y7" s="16">
         <v>17</v>
       </c>
-      <c r="Z7" s="25">
+      <c r="Z7" s="16">
         <v>100</v>
       </c>
-      <c r="AA7" s="25">
+      <c r="AA7" s="16">
         <v>20</v>
       </c>
-      <c r="AB7" s="25">
+      <c r="AB7" s="16">
         <v>26</v>
       </c>
-      <c r="AC7" s="25">
+      <c r="AC7" s="16">
         <v>11</v>
       </c>
-      <c r="AD7" s="25">
+      <c r="AD7" s="16">
         <v>40</v>
       </c>
-      <c r="AE7" s="25">
+      <c r="AE7" s="16">
         <v>45</v>
       </c>
-      <c r="AF7" s="25"/>
-      <c r="AG7" s="26"/>
+      <c r="AF7" s="16"/>
+      <c r="AG7" s="17"/>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A8" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="23">
+      <c r="B8" s="68"/>
+      <c r="C8" s="14">
         <v>7.44</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="14">
         <v>6.6650010000000002</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="14">
         <v>6.665</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="14">
         <v>7.3768539999999998</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="14">
         <v>6.780125</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="14">
         <v>7.728523</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="14">
         <v>7.3231999999999999</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="14">
         <v>7.44</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="14">
         <v>7.3</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="14">
         <v>6.8</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="14">
         <v>7.62</v>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="14">
         <v>6.2400010000000004</v>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="14">
         <v>6.5700029999999998</v>
       </c>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="24">
+      <c r="P8" s="14"/>
+      <c r="Q8" s="15">
         <v>8.3448840000000004</v>
       </c>
-      <c r="R8" s="24"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="25"/>
-      <c r="X8" s="25"/>
-      <c r="Y8" s="25"/>
-      <c r="Z8" s="25"/>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="25"/>
-      <c r="AC8" s="25"/>
-      <c r="AD8" s="25"/>
-      <c r="AE8" s="25"/>
-      <c r="AF8" s="25"/>
-      <c r="AG8" s="26"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="17"/>
     </row>
-    <row r="9" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+    <row r="9" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="14" t="s">
+      <c r="B9" s="68"/>
+      <c r="C9" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="20" t="s">
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="Q9" s="15" t="s">
+      <c r="Q9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="R9" s="15" t="s">
+      <c r="R9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="S9" s="17" t="s">
+      <c r="S9" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17"/>
-      <c r="AB9" s="17"/>
-      <c r="AC9" s="17"/>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="17"/>
-      <c r="AF9" s="21" t="s">
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="71"/>
+      <c r="X9" s="71"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="71"/>
+      <c r="AA9" s="71"/>
+      <c r="AB9" s="71"/>
+      <c r="AC9" s="71"/>
+      <c r="AD9" s="71"/>
+      <c r="AE9" s="71"/>
+      <c r="AF9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AG9" s="22" t="s">
+      <c r="AG9" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="68"/>
+      <c r="C10" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="20" t="s">
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="75"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="75"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="75"/>
+      <c r="P10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="Q10" s="15" t="s">
+      <c r="Q10" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="R10" s="15" t="s">
+      <c r="R10" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="S10" s="17" t="s">
+      <c r="S10" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17"/>
-      <c r="AB10" s="17"/>
-      <c r="AC10" s="17"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="17"/>
-      <c r="AF10" s="21" t="s">
+      <c r="T10" s="71"/>
+      <c r="U10" s="71"/>
+      <c r="V10" s="71"/>
+      <c r="W10" s="71"/>
+      <c r="X10" s="71"/>
+      <c r="Y10" s="71"/>
+      <c r="Z10" s="71"/>
+      <c r="AA10" s="71"/>
+      <c r="AB10" s="71"/>
+      <c r="AC10" s="71"/>
+      <c r="AD10" s="71"/>
+      <c r="AE10" s="71"/>
+      <c r="AF10" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AG10" s="22" t="s">
+      <c r="AG10" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A11" s="68">
         <v>46136</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="27">
+      <c r="B11" s="68"/>
+      <c r="C11" s="18">
         <v>301937</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="18">
         <v>34824</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="18">
         <v>139513</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="18">
         <v>22291</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="18">
         <v>4606</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="18">
         <v>1947.5619999999999</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="18">
         <v>190906</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="18">
         <v>156771.1</v>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="18">
         <v>53403.38</v>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="18">
         <v>13962</v>
       </c>
-      <c r="M11" s="27">
+      <c r="M11" s="18">
         <v>325872</v>
       </c>
-      <c r="N11" s="27">
+      <c r="N11" s="18">
         <v>7164</v>
       </c>
-      <c r="O11" s="27">
+      <c r="O11" s="18">
         <v>4620</v>
       </c>
-      <c r="P11" s="28">
+      <c r="P11" s="19">
         <v>149743.85290999999</v>
       </c>
-      <c r="Q11" s="29">
-        <v>0</v>
-      </c>
-      <c r="R11" s="30">
-        <v>0</v>
-      </c>
-      <c r="S11" s="31">
+      <c r="Q11" s="20">
+        <v>0</v>
+      </c>
+      <c r="R11" s="21">
+        <v>0</v>
+      </c>
+      <c r="S11" s="22">
         <v>14.2872521</v>
       </c>
-      <c r="T11" s="31">
+      <c r="T11" s="22">
         <v>0.44900000000000001</v>
       </c>
-      <c r="U11" s="31">
+      <c r="U11" s="22">
         <v>1E-3</v>
       </c>
-      <c r="V11" s="31">
+      <c r="V11" s="22">
         <v>3.8314E-3</v>
       </c>
-      <c r="W11" s="32">
-        <v>0</v>
-      </c>
-      <c r="X11" s="31">
+      <c r="W11" s="23">
+        <v>0</v>
+      </c>
+      <c r="X11" s="22">
         <v>11.323371099999999</v>
       </c>
-      <c r="Y11" s="31">
+      <c r="Y11" s="22">
         <v>3.3338809999999999</v>
       </c>
-      <c r="Z11" s="31">
+      <c r="Z11" s="22">
         <v>0.27339999999999998</v>
       </c>
-      <c r="AA11" s="31">
+      <c r="AA11" s="22">
         <v>10.295478900000001</v>
       </c>
-      <c r="AB11" s="31">
+      <c r="AB11" s="22">
         <v>9.7127490000000005</v>
       </c>
-      <c r="AC11" s="31">
+      <c r="AC11" s="22">
         <v>0.20169970000000001</v>
       </c>
-      <c r="AD11" s="31">
+      <c r="AD11" s="22">
         <v>8.3909300000000006E-2</v>
       </c>
-      <c r="AE11" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="25">
+      <c r="AE11" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="16">
         <v>7.9471104879250003</v>
       </c>
-      <c r="AG11" s="33">
+      <c r="AG11" s="24">
         <v>199731.17787904799</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A12" s="68">
         <v>46137</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="34">
+      <c r="B12" s="68"/>
+      <c r="C12" s="25">
         <v>315426</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="25">
         <v>34906</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="20">
         <v>139513</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="25">
         <v>7279</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="25">
         <v>4601</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="25">
         <v>1937</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="25">
         <v>191093</v>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="25">
         <v>155569.9</v>
       </c>
-      <c r="K12" s="34">
+      <c r="K12" s="25">
         <v>53342.21</v>
       </c>
-      <c r="L12" s="34">
+      <c r="L12" s="25">
         <v>12371</v>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="25">
         <v>444293</v>
       </c>
-      <c r="N12" s="34">
+      <c r="N12" s="25">
         <v>7223</v>
       </c>
-      <c r="O12" s="34">
+      <c r="O12" s="25">
         <v>4739</v>
       </c>
-      <c r="P12" s="28">
+      <c r="P12" s="19">
         <v>143755.98091000001</v>
       </c>
-      <c r="Q12" s="29">
-        <v>0</v>
-      </c>
-      <c r="R12" s="30">
-        <v>0</v>
-      </c>
-      <c r="S12" s="35">
+      <c r="Q12" s="20">
+        <v>0</v>
+      </c>
+      <c r="R12" s="21">
+        <v>0</v>
+      </c>
+      <c r="S12" s="26">
         <v>14.3164306</v>
       </c>
-      <c r="T12" s="35">
+      <c r="T12" s="26">
         <v>0.44700000000000001</v>
       </c>
-      <c r="U12" s="32">
+      <c r="U12" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V12" s="35">
+      <c r="V12" s="26">
         <v>1.2895000000000001E-3</v>
       </c>
-      <c r="W12" s="32">
-        <v>0</v>
-      </c>
-      <c r="X12" s="35">
+      <c r="W12" s="23">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26">
         <v>11.3055524</v>
       </c>
-      <c r="Y12" s="35">
+      <c r="Y12" s="26">
         <v>3.3321812999999998</v>
       </c>
-      <c r="Z12" s="35">
+      <c r="Z12" s="26">
         <v>0.28131</v>
       </c>
-      <c r="AA12" s="35">
+      <c r="AA12" s="26">
         <v>10.174849200000001</v>
       </c>
-      <c r="AB12" s="35">
+      <c r="AB12" s="26">
         <v>9.6641019999999997</v>
       </c>
-      <c r="AC12" s="35">
+      <c r="AC12" s="26">
         <v>0.1963173</v>
       </c>
-      <c r="AD12" s="35">
+      <c r="AD12" s="26">
         <v>9.2662900000000006E-2</v>
       </c>
-      <c r="AE12" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="25">
+      <c r="AE12" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="16">
         <v>7.9163717170499996</v>
       </c>
-      <c r="AG12" s="33">
+      <c r="AG12" s="24">
         <v>193549.959010244</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A13" s="68">
         <v>46138</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="27">
+      <c r="B13" s="68"/>
+      <c r="C13" s="18">
         <v>328888</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="18">
         <v>34780</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="20">
         <v>139513</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="18">
         <v>1204</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="18">
         <v>4610</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="18">
         <v>1933</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="18">
         <v>191415</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="18">
         <v>153893</v>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="18">
         <v>53760.29</v>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="18">
         <v>14339</v>
       </c>
-      <c r="M13" s="27">
+      <c r="M13" s="18">
         <v>463730</v>
       </c>
-      <c r="N13" s="27">
+      <c r="N13" s="18">
         <v>7219</v>
       </c>
-      <c r="O13" s="27">
+      <c r="O13" s="18">
         <v>4825</v>
       </c>
-      <c r="P13" s="28">
+      <c r="P13" s="19">
         <v>140882.87041</v>
       </c>
-      <c r="Q13" s="29">
-        <v>0</v>
-      </c>
-      <c r="R13" s="30">
-        <v>0</v>
-      </c>
-      <c r="S13" s="31">
+      <c r="Q13" s="20">
+        <v>0</v>
+      </c>
+      <c r="R13" s="21">
+        <v>0</v>
+      </c>
+      <c r="S13" s="22">
         <v>14.333710999999999</v>
       </c>
-      <c r="T13" s="31">
+      <c r="T13" s="22">
         <v>0.44800000000000001</v>
       </c>
-      <c r="U13" s="32">
+      <c r="U13" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V13" s="31">
+      <c r="V13" s="22">
         <v>6.6649999999999999E-4</v>
       </c>
-      <c r="W13" s="32">
-        <v>0</v>
-      </c>
-      <c r="X13" s="31">
+      <c r="W13" s="23">
+        <v>0</v>
+      </c>
+      <c r="X13" s="22">
         <v>11.2907365</v>
       </c>
-      <c r="Y13" s="31">
+      <c r="Y13" s="22">
         <v>3.3372804999999999</v>
       </c>
-      <c r="Z13" s="31">
+      <c r="Z13" s="22">
         <v>0.27564</v>
       </c>
-      <c r="AA13" s="31">
+      <c r="AA13" s="22">
         <v>10.1869689</v>
       </c>
-      <c r="AB13" s="31">
+      <c r="AB13" s="22">
         <v>9.5919509999999999</v>
       </c>
-      <c r="AC13" s="31">
+      <c r="AC13" s="22">
         <v>0.20056660000000001</v>
       </c>
-      <c r="AD13" s="31">
+      <c r="AD13" s="22">
         <v>9.3116099999999993E-2</v>
       </c>
-      <c r="AE13" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="25">
+      <c r="AE13" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="16">
         <v>7.8937026127500003</v>
       </c>
-      <c r="AG13" s="33">
+      <c r="AG13" s="24">
         <v>190534.25984419699</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A14" s="68">
         <v>46139</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="34">
+      <c r="B14" s="68"/>
+      <c r="C14" s="25">
         <v>302967</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="25">
         <v>36195</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="20">
         <v>139513</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="25">
         <v>1221</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="25">
         <v>4507</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="25">
         <v>1886</v>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="25">
         <v>191366</v>
       </c>
-      <c r="J14" s="34">
+      <c r="J14" s="25">
         <v>156214.1</v>
       </c>
-      <c r="K14" s="34">
+      <c r="K14" s="25">
         <v>53017.86</v>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="25">
         <v>13763</v>
       </c>
-      <c r="M14" s="34">
+      <c r="M14" s="25">
         <v>455890</v>
       </c>
-      <c r="N14" s="34">
+      <c r="N14" s="25">
         <v>7227</v>
       </c>
-      <c r="O14" s="34">
+      <c r="O14" s="25">
         <v>4884</v>
       </c>
-      <c r="P14" s="28">
+      <c r="P14" s="19">
         <v>140400.12966000001</v>
       </c>
-      <c r="Q14" s="29">
-        <v>0</v>
-      </c>
-      <c r="R14" s="30">
-        <v>0</v>
-      </c>
-      <c r="S14" s="35">
+      <c r="Q14" s="20">
+        <v>0</v>
+      </c>
+      <c r="R14" s="21">
+        <v>0</v>
+      </c>
+      <c r="S14" s="26">
         <v>14.3062323</v>
       </c>
-      <c r="T14" s="35">
+      <c r="T14" s="26">
         <v>0.44900000000000001</v>
       </c>
-      <c r="U14" s="32">
+      <c r="U14" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V14" s="35">
+      <c r="V14" s="26">
         <v>6.5890000000000002E-4</v>
       </c>
-      <c r="W14" s="32">
-        <v>0</v>
-      </c>
-      <c r="X14" s="35">
+      <c r="W14" s="23">
+        <v>0</v>
+      </c>
+      <c r="X14" s="26">
         <v>11.296034000000001</v>
       </c>
-      <c r="Y14" s="35">
+      <c r="Y14" s="26">
         <v>3.3401415999999999</v>
       </c>
-      <c r="Z14" s="35">
+      <c r="Z14" s="26">
         <v>0.27246999999999999</v>
       </c>
-      <c r="AA14" s="35">
+      <c r="AA14" s="26">
         <v>10.5833756</v>
       </c>
-      <c r="AB14" s="35">
+      <c r="AB14" s="26">
         <v>9.4546720000000004</v>
       </c>
-      <c r="AC14" s="35">
+      <c r="AC14" s="26">
         <v>0.19886690000000001</v>
       </c>
-      <c r="AD14" s="35">
+      <c r="AD14" s="26">
         <v>8.6430599999999996E-2</v>
       </c>
-      <c r="AE14" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="25">
+      <c r="AE14" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="16">
         <v>7.9321081357749996</v>
       </c>
-      <c r="AG14" s="33">
+      <c r="AG14" s="24">
         <v>190293.08983402399</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A15" s="68">
         <v>46140</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="27">
+      <c r="B15" s="68"/>
+      <c r="C15" s="18">
         <v>306082</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="18">
         <v>34233</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="20">
         <v>139513</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="18">
         <v>18087</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="18">
         <v>4376</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="18">
         <v>1911</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="18">
         <v>187214</v>
       </c>
-      <c r="J15" s="27">
+      <c r="J15" s="18">
         <v>151675.70000000001</v>
       </c>
-      <c r="K15" s="27">
+      <c r="K15" s="18">
         <v>53261.98</v>
       </c>
-      <c r="L15" s="27">
+      <c r="L15" s="18">
         <v>13725</v>
       </c>
-      <c r="M15" s="27">
+      <c r="M15" s="18">
         <v>470527</v>
       </c>
-      <c r="N15" s="27">
+      <c r="N15" s="18">
         <v>7228</v>
       </c>
-      <c r="O15" s="27">
+      <c r="O15" s="18">
         <v>4928</v>
       </c>
-      <c r="P15" s="28">
+      <c r="P15" s="19">
         <v>150371.87190999999</v>
       </c>
-      <c r="Q15" s="29">
-        <v>0</v>
-      </c>
-      <c r="R15" s="30">
-        <v>0</v>
-      </c>
-      <c r="S15" s="31">
+      <c r="Q15" s="20">
+        <v>0</v>
+      </c>
+      <c r="R15" s="21">
+        <v>0</v>
+      </c>
+      <c r="S15" s="22">
         <v>14.6631728</v>
       </c>
-      <c r="T15" s="31">
+      <c r="T15" s="22">
         <v>0.45</v>
       </c>
-      <c r="U15" s="32">
+      <c r="U15" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V15" s="31">
+      <c r="V15" s="22">
         <v>2.3938000000000002E-3</v>
       </c>
-      <c r="W15" s="32">
-        <v>0</v>
-      </c>
-      <c r="X15" s="31">
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="22">
         <v>11.333824399999999</v>
       </c>
-      <c r="Y15" s="31">
+      <c r="Y15" s="22">
         <v>3.3334277999999999</v>
       </c>
-      <c r="Z15" s="31">
+      <c r="Z15" s="22">
         <v>0.27195000000000003</v>
       </c>
-      <c r="AA15" s="31">
+      <c r="AA15" s="22">
         <v>10.4185436</v>
       </c>
-      <c r="AB15" s="31">
+      <c r="AB15" s="22">
         <v>9.4238710000000001</v>
       </c>
-      <c r="AC15" s="31">
+      <c r="AC15" s="22">
         <v>0.19943340000000001</v>
       </c>
-      <c r="AD15" s="31">
+      <c r="AD15" s="22">
         <v>9.3541100000000002E-2</v>
       </c>
-      <c r="AE15" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="25">
+      <c r="AE15" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="16">
         <v>7.9107279524000003</v>
       </c>
-      <c r="AG15" s="33">
+      <c r="AG15" s="24">
         <v>200130.35073059599</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A16" s="68">
         <v>46141</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="34">
+      <c r="B16" s="68"/>
+      <c r="C16" s="25">
         <v>328909</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="25">
         <v>34912</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="20">
         <v>139513</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="25">
         <v>22417</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="25">
         <v>4375</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="25">
         <v>1933</v>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="25">
         <v>186261</v>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="25">
         <v>154613.20000000001</v>
       </c>
-      <c r="K16" s="34">
+      <c r="K16" s="25">
         <v>53126.55</v>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="25">
         <v>12515</v>
       </c>
-      <c r="M16" s="34">
+      <c r="M16" s="25">
         <v>459253</v>
       </c>
-      <c r="N16" s="34">
+      <c r="N16" s="25">
         <v>7283</v>
       </c>
-      <c r="O16" s="34">
+      <c r="O16" s="25">
         <v>5837</v>
       </c>
-      <c r="P16" s="28">
+      <c r="P16" s="19">
         <v>154441.46166</v>
       </c>
-      <c r="Q16" s="29">
-        <v>0</v>
-      </c>
-      <c r="R16" s="30">
-        <v>0</v>
-      </c>
-      <c r="S16" s="35">
+      <c r="Q16" s="20">
+        <v>0</v>
+      </c>
+      <c r="R16" s="21">
+        <v>0</v>
+      </c>
+      <c r="S16" s="26">
         <v>14.6441926</v>
       </c>
-      <c r="T16" s="35">
+      <c r="T16" s="26">
         <v>0.44800000000000001</v>
       </c>
-      <c r="U16" s="32">
+      <c r="U16" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V16" s="35">
+      <c r="V16" s="26">
         <v>3.2780000000000001E-3</v>
       </c>
-      <c r="W16" s="32">
-        <v>0</v>
-      </c>
-      <c r="X16" s="35">
+      <c r="W16" s="23">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26">
         <v>11.341671399999999</v>
       </c>
-      <c r="Y16" s="35">
+      <c r="Y16" s="26">
         <v>3.3277337</v>
       </c>
-      <c r="Z16" s="35">
+      <c r="Z16" s="26">
         <v>0.28100000000000003</v>
       </c>
-      <c r="AA16" s="35">
+      <c r="AA16" s="26">
         <v>10.289928700000001</v>
       </c>
-      <c r="AB16" s="35">
+      <c r="AB16" s="26">
         <v>9.8929819999999999</v>
       </c>
-      <c r="AC16" s="35">
+      <c r="AC16" s="26">
         <v>0.20311609999999999</v>
       </c>
-      <c r="AD16" s="35">
+      <c r="AD16" s="26">
         <v>9.2351299999999997E-2</v>
       </c>
-      <c r="AE16" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="25">
+      <c r="AE16" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="16">
         <v>8.01584277155</v>
       </c>
-      <c r="AG16" s="33">
+      <c r="AG16" s="24">
         <v>204861.11269304901</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A17" s="68">
         <v>46142</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="27">
+      <c r="B17" s="68"/>
+      <c r="C17" s="18">
         <v>322311</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="18">
         <v>34893</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="18">
         <v>139513</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="18">
         <v>22580</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="18">
         <v>4371</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="18">
         <v>1895</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="18">
         <v>191380</v>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="18">
         <v>154987.70000000001</v>
       </c>
-      <c r="K17" s="27">
+      <c r="K17" s="18">
         <v>54088.59</v>
       </c>
-      <c r="L17" s="27">
+      <c r="L17" s="18">
         <v>13981</v>
       </c>
-      <c r="M17" s="27">
+      <c r="M17" s="18">
         <v>460584</v>
       </c>
-      <c r="N17" s="27">
+      <c r="N17" s="18">
         <v>7324</v>
       </c>
-      <c r="O17" s="27">
+      <c r="O17" s="18">
         <v>5125</v>
       </c>
-      <c r="P17" s="28">
+      <c r="P17" s="19">
         <v>155805.74265999999</v>
       </c>
-      <c r="Q17" s="29">
-        <v>0</v>
-      </c>
-      <c r="R17" s="30">
-        <v>0</v>
-      </c>
-      <c r="S17" s="31">
+      <c r="Q17" s="20">
+        <v>0</v>
+      </c>
+      <c r="R17" s="21">
+        <v>0</v>
+      </c>
+      <c r="S17" s="22">
         <v>14.4050992</v>
       </c>
-      <c r="T17" s="31">
+      <c r="T17" s="22">
         <v>0.45700000000000002</v>
       </c>
-      <c r="U17" s="31">
+      <c r="U17" s="22">
         <v>1E-3</v>
       </c>
-      <c r="V17" s="31">
+      <c r="V17" s="22">
         <v>3.7678E-3</v>
       </c>
-      <c r="W17" s="32">
-        <v>0</v>
-      </c>
-      <c r="X17" s="31">
+      <c r="W17" s="23">
+        <v>0</v>
+      </c>
+      <c r="X17" s="22">
         <v>11.0150142</v>
       </c>
-      <c r="Y17" s="31">
+      <c r="Y17" s="22">
         <v>3.3227194999999998</v>
       </c>
-      <c r="Z17" s="31">
+      <c r="Z17" s="22">
         <v>0.27544000000000002</v>
       </c>
-      <c r="AA17" s="31">
+      <c r="AA17" s="22">
         <v>10.5116209</v>
       </c>
-      <c r="AB17" s="31">
+      <c r="AB17" s="22">
         <v>10.072462</v>
       </c>
-      <c r="AC17" s="31">
+      <c r="AC17" s="22">
         <v>0.20368269999999999</v>
       </c>
-      <c r="AD17" s="31">
+      <c r="AD17" s="22">
         <v>8.9433399999999996E-2</v>
       </c>
-      <c r="AE17" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="25">
+      <c r="AE17" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="16">
         <v>8.0395764175999993</v>
       </c>
-      <c r="AG17" s="33">
+      <c r="AG17" s="24">
         <v>206374.67832670399</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A18" s="68">
         <v>46143</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="34">
+      <c r="B18" s="68"/>
+      <c r="C18" s="25">
         <v>329110</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="25">
         <v>35025</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="20">
         <v>139513</v>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="25">
         <v>9102</v>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="25">
         <v>4345</v>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="25">
         <v>1917</v>
       </c>
-      <c r="I18" s="34">
+      <c r="I18" s="25">
         <v>189393</v>
       </c>
-      <c r="J18" s="34">
+      <c r="J18" s="25">
         <v>153956.5</v>
       </c>
-      <c r="K18" s="34">
+      <c r="K18" s="25">
         <v>53842.32</v>
       </c>
-      <c r="L18" s="34">
+      <c r="L18" s="25">
         <v>14776</v>
       </c>
-      <c r="M18" s="34">
+      <c r="M18" s="25">
         <v>423906</v>
       </c>
-      <c r="N18" s="34">
+      <c r="N18" s="25">
         <v>7073</v>
       </c>
-      <c r="O18" s="34">
+      <c r="O18" s="25">
         <v>5342</v>
       </c>
-      <c r="P18" s="28">
+      <c r="P18" s="19">
         <v>144671.43766</v>
       </c>
-      <c r="Q18" s="29">
-        <v>0</v>
-      </c>
-      <c r="R18" s="30">
-        <v>0</v>
-      </c>
-      <c r="S18" s="35">
+      <c r="Q18" s="20">
+        <v>0</v>
+      </c>
+      <c r="R18" s="21">
+        <v>0</v>
+      </c>
+      <c r="S18" s="26">
         <v>14.2090652</v>
       </c>
-      <c r="T18" s="35">
+      <c r="T18" s="26">
         <v>0.47299999999999998</v>
       </c>
-      <c r="U18" s="32">
+      <c r="U18" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V18" s="35">
+      <c r="V18" s="26">
         <v>1.6718E-3</v>
       </c>
-      <c r="W18" s="32">
-        <v>0</v>
-      </c>
-      <c r="X18" s="35">
+      <c r="W18" s="23">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26">
         <v>11.358186999999999</v>
       </c>
-      <c r="Y18" s="35">
+      <c r="Y18" s="26">
         <v>3.3200566999999999</v>
       </c>
-      <c r="Z18" s="35">
+      <c r="Z18" s="26">
         <v>0.28175099999999997</v>
       </c>
-      <c r="AA18" s="35">
+      <c r="AA18" s="26">
         <v>8.5675592999999992</v>
       </c>
-      <c r="AB18" s="35">
+      <c r="AB18" s="26">
         <v>10.083168000000001</v>
       </c>
-      <c r="AC18" s="35">
+      <c r="AC18" s="26">
         <v>0.1997167</v>
       </c>
-      <c r="AD18" s="35">
+      <c r="AD18" s="26">
         <v>9.52408E-2</v>
       </c>
-      <c r="AE18" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="25">
+      <c r="AE18" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="16">
         <v>7.7167508630999997</v>
       </c>
-      <c r="AG18" s="33">
+      <c r="AG18" s="24">
         <v>193209.800588899</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A19" s="68">
         <v>46144</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="27">
+      <c r="B19" s="68"/>
+      <c r="C19" s="18">
         <v>325172</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="18">
         <v>34843</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="20">
         <v>139513</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="18">
         <v>22316</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="18">
         <v>4155</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="18">
         <v>1878</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="18">
         <v>187915</v>
       </c>
-      <c r="J19" s="27">
+      <c r="J19" s="18">
         <v>153981.5</v>
       </c>
-      <c r="K19" s="27">
+      <c r="K19" s="18">
         <v>53498.61</v>
       </c>
-      <c r="L19" s="27">
+      <c r="L19" s="18">
         <v>13054</v>
       </c>
-      <c r="M19" s="27">
+      <c r="M19" s="18">
         <v>438894</v>
       </c>
-      <c r="N19" s="27">
+      <c r="N19" s="18">
         <v>7084</v>
       </c>
-      <c r="O19" s="27">
+      <c r="O19" s="18">
         <v>5113</v>
       </c>
-      <c r="P19" s="28">
+      <c r="P19" s="19">
         <v>153341.58116</v>
       </c>
-      <c r="Q19" s="29">
-        <v>0</v>
-      </c>
-      <c r="R19" s="30">
-        <v>0</v>
-      </c>
-      <c r="S19" s="31">
+      <c r="Q19" s="20">
+        <v>0</v>
+      </c>
+      <c r="R19" s="21">
+        <v>0</v>
+      </c>
+      <c r="S19" s="22">
         <v>14.2597734</v>
       </c>
-      <c r="T19" s="31">
+      <c r="T19" s="22">
         <v>0.47799999999999998</v>
       </c>
-      <c r="U19" s="32">
+      <c r="U19" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V19" s="31">
+      <c r="V19" s="22">
         <v>3.2246000000000002E-3</v>
       </c>
-      <c r="W19" s="32">
-        <v>0</v>
-      </c>
-      <c r="X19" s="31">
+      <c r="W19" s="23">
+        <v>0</v>
+      </c>
+      <c r="X19" s="22">
         <v>11.3327762</v>
       </c>
-      <c r="Y19" s="31">
+      <c r="Y19" s="22">
         <v>3.3182436000000002</v>
       </c>
-      <c r="Z19" s="31">
+      <c r="Z19" s="22">
         <v>0.27155299999999999</v>
       </c>
-      <c r="AA19" s="31">
+      <c r="AA19" s="22">
         <v>8.531682</v>
       </c>
-      <c r="AB19" s="31">
+      <c r="AB19" s="22">
         <v>10.134039</v>
       </c>
-      <c r="AC19" s="31">
+      <c r="AC19" s="22">
         <v>0.19773370000000001</v>
       </c>
-      <c r="AD19" s="31">
+      <c r="AD19" s="22">
         <v>8.5807400000000006E-2</v>
       </c>
-      <c r="AE19" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="25">
+      <c r="AE19" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="16">
         <v>7.7079044849500002</v>
       </c>
-      <c r="AG19" s="33">
+      <c r="AG19" s="24">
         <v>201824.300370335</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A20" s="68">
         <v>46145</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="34">
+      <c r="B20" s="68"/>
+      <c r="C20" s="25">
         <v>333126</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="25">
         <v>35157</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="20">
         <v>139513</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="25">
         <v>22377.66</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="25">
         <v>4166</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="25">
         <v>1918</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="25">
         <v>188996</v>
       </c>
-      <c r="J20" s="34">
+      <c r="J20" s="25">
         <v>155364.20000000001</v>
       </c>
-      <c r="K20" s="34">
+      <c r="K20" s="25">
         <v>54978.91</v>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="25">
         <v>11182</v>
       </c>
-      <c r="M20" s="34">
+      <c r="M20" s="25">
         <v>424183</v>
       </c>
-      <c r="N20" s="34">
+      <c r="N20" s="25">
         <v>6841</v>
       </c>
-      <c r="O20" s="34">
+      <c r="O20" s="25">
         <v>5242</v>
       </c>
-      <c r="P20" s="28">
+      <c r="P20" s="19">
         <v>153678.26465999999</v>
       </c>
-      <c r="Q20" s="29">
-        <v>0</v>
-      </c>
-      <c r="R20" s="30">
-        <v>0</v>
-      </c>
-      <c r="S20" s="35">
+      <c r="Q20" s="20">
+        <v>0</v>
+      </c>
+      <c r="R20" s="21">
+        <v>0</v>
+      </c>
+      <c r="S20" s="26">
         <v>14.138243599999999</v>
       </c>
-      <c r="T20" s="35">
+      <c r="T20" s="26">
         <v>0.48799999999999999</v>
       </c>
-      <c r="U20" s="32">
+      <c r="U20" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V20" s="35">
+      <c r="V20" s="26">
         <v>3.5872E-3</v>
       </c>
-      <c r="W20" s="32">
-        <v>0</v>
-      </c>
-      <c r="X20" s="35">
+      <c r="W20" s="23">
+        <v>0</v>
+      </c>
+      <c r="X20" s="26">
         <v>11.2974221</v>
       </c>
-      <c r="Y20" s="35">
+      <c r="Y20" s="26">
         <v>3.3205949000000001</v>
       </c>
-      <c r="Z20" s="35">
+      <c r="Z20" s="26">
         <v>0.28052899999999997</v>
       </c>
-      <c r="AA20" s="35">
+      <c r="AA20" s="26">
         <v>8.5388461000000007</v>
       </c>
-      <c r="AB20" s="35">
+      <c r="AB20" s="26">
         <v>10.096508</v>
       </c>
-      <c r="AC20" s="35">
+      <c r="AC20" s="26">
         <v>0.1946176</v>
       </c>
-      <c r="AD20" s="35">
+      <c r="AD20" s="26">
         <v>9.2776200000000003E-2</v>
       </c>
-      <c r="AE20" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="25">
+      <c r="AE20" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="16">
         <v>7.7047885912999998</v>
       </c>
-      <c r="AG20" s="33">
+      <c r="AG20" s="24">
         <v>202141.38489927701</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A21" s="68">
         <v>46146</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="27">
+      <c r="B21" s="68"/>
+      <c r="C21" s="18">
         <v>333108</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="18">
         <v>35308</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="20">
         <v>139513</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="18">
         <v>22357.599999999999</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="18">
         <v>4176</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="18">
         <v>1922</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="18">
         <v>190834</v>
       </c>
-      <c r="J21" s="27">
+      <c r="J21" s="18">
         <v>156530.20000000001</v>
       </c>
-      <c r="K21" s="27">
+      <c r="K21" s="18">
         <v>53766.879999999997</v>
       </c>
-      <c r="L21" s="27">
+      <c r="L21" s="18">
         <v>13768</v>
       </c>
-      <c r="M21" s="27">
+      <c r="M21" s="18">
         <v>273777</v>
       </c>
-      <c r="N21" s="27">
+      <c r="N21" s="18">
         <v>6848</v>
       </c>
-      <c r="O21" s="27">
+      <c r="O21" s="18">
         <v>5121</v>
       </c>
-      <c r="P21" s="28">
+      <c r="P21" s="19">
         <v>148641.22115999999</v>
       </c>
-      <c r="Q21" s="29">
-        <v>0</v>
-      </c>
-      <c r="R21" s="30">
-        <v>0</v>
-      </c>
-      <c r="S21" s="31">
+      <c r="Q21" s="20">
+        <v>0</v>
+      </c>
+      <c r="R21" s="21">
+        <v>0</v>
+      </c>
+      <c r="S21" s="22">
         <v>14.232011099999999</v>
       </c>
-      <c r="T21" s="31">
+      <c r="T21" s="22">
         <v>0.496</v>
       </c>
-      <c r="U21" s="32">
+      <c r="U21" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="22">
         <v>3.4773999999999998E-3</v>
       </c>
-      <c r="W21" s="32">
-        <v>0</v>
-      </c>
-      <c r="X21" s="31">
+      <c r="W21" s="23">
+        <v>0</v>
+      </c>
+      <c r="X21" s="22">
         <v>11.3142493</v>
       </c>
-      <c r="Y21" s="31">
+      <c r="Y21" s="22">
         <v>3.3223229000000001</v>
       </c>
-      <c r="Z21" s="31">
+      <c r="Z21" s="22">
         <v>0.27085700000000001</v>
       </c>
-      <c r="AA21" s="31">
+      <c r="AA21" s="22">
         <v>8.5319368000000004</v>
       </c>
-      <c r="AB21" s="31">
+      <c r="AB21" s="22">
         <v>10.001754999999999</v>
       </c>
-      <c r="AC21" s="31">
+      <c r="AC21" s="22">
         <v>0.19546740000000001</v>
       </c>
-      <c r="AD21" s="31">
+      <c r="AD21" s="22">
         <v>8.7223800000000004E-2</v>
       </c>
-      <c r="AE21" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="25">
+      <c r="AE21" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="16">
         <v>7.6749516926750001</v>
       </c>
-      <c r="AG21" s="33">
+      <c r="AG21" s="24">
         <v>196916.667306925</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" s="19">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A22" s="68">
         <v>46147</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="34">
+      <c r="B22" s="68"/>
+      <c r="C22" s="25">
         <v>332006</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="25">
         <v>34950</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="20">
         <v>139513</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="25">
         <v>22322</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="25">
         <v>4224</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="25">
         <v>1910</v>
       </c>
-      <c r="I22" s="34">
+      <c r="I22" s="25">
         <v>190757</v>
       </c>
-      <c r="J22" s="34">
+      <c r="J22" s="25">
         <v>158520.4</v>
       </c>
-      <c r="K22" s="34">
+      <c r="K22" s="25">
         <v>54310.39</v>
       </c>
-      <c r="L22" s="34">
+      <c r="L22" s="25">
         <v>11773</v>
       </c>
-      <c r="M22" s="34">
+      <c r="M22" s="25">
         <v>165947</v>
       </c>
-      <c r="N22" s="34">
+      <c r="N22" s="25">
         <v>6655</v>
       </c>
-      <c r="O22" s="34">
+      <c r="O22" s="25">
         <v>5169</v>
       </c>
-      <c r="P22" s="28">
+      <c r="P22" s="19">
         <v>144340.81341</v>
       </c>
-      <c r="Q22" s="29">
-        <v>0</v>
-      </c>
-      <c r="R22" s="30">
-        <v>0</v>
-      </c>
-      <c r="S22" s="35">
+      <c r="Q22" s="20">
+        <v>0</v>
+      </c>
+      <c r="R22" s="21">
+        <v>0</v>
+      </c>
+      <c r="S22" s="26">
         <v>14.1626064</v>
       </c>
-      <c r="T22" s="35">
+      <c r="T22" s="26">
         <v>0.5</v>
       </c>
-      <c r="U22" s="32">
+      <c r="U22" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V22" s="35">
+      <c r="V22" s="26">
         <v>3.6216E-3</v>
       </c>
-      <c r="W22" s="32">
-        <v>0</v>
-      </c>
-      <c r="X22" s="35">
+      <c r="W22" s="23">
+        <v>0</v>
+      </c>
+      <c r="X22" s="26">
         <v>11.317960299999999</v>
       </c>
-      <c r="Y22" s="35">
+      <c r="Y22" s="26">
         <v>3.3226629000000001</v>
       </c>
-      <c r="Z22" s="35">
+      <c r="Z22" s="26">
         <v>0.28170099999999998</v>
       </c>
-      <c r="AA22" s="35">
+      <c r="AA22" s="26">
         <v>8.5196755999999993</v>
       </c>
-      <c r="AB22" s="35">
+      <c r="AB22" s="26">
         <v>9.6571210000000001</v>
       </c>
-      <c r="AC22" s="35">
+      <c r="AC22" s="26">
         <v>0.194051</v>
       </c>
-      <c r="AD22" s="35">
+      <c r="AD22" s="26">
         <v>9.9660100000000001E-2</v>
       </c>
-      <c r="AE22" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="25">
+      <c r="AE22" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="16">
         <v>7.5983968512000004</v>
       </c>
-      <c r="AG22" s="33">
+      <c r="AG22" s="24">
         <v>192134.72960404801</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" s="19">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A23" s="68">
         <v>46148</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="27">
+      <c r="B23" s="68"/>
+      <c r="C23" s="18">
         <v>307722</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="18">
         <v>32459</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="20">
         <v>139513</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="18">
         <v>22239</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="18">
         <v>4232</v>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="18">
         <v>1935</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="18">
         <v>190556</v>
       </c>
-      <c r="J23" s="27">
+      <c r="J23" s="18">
         <v>154463.1</v>
       </c>
-      <c r="K23" s="27">
+      <c r="K23" s="18">
         <v>53960.99</v>
       </c>
-      <c r="L23" s="27">
+      <c r="L23" s="18">
         <v>13005</v>
       </c>
-      <c r="M23" s="27">
+      <c r="M23" s="18">
         <v>77474</v>
       </c>
-      <c r="N23" s="27">
+      <c r="N23" s="18">
         <v>6925</v>
       </c>
-      <c r="O23" s="27">
+      <c r="O23" s="18">
         <v>5223</v>
       </c>
-      <c r="P23" s="28">
+      <c r="P23" s="19">
         <v>138555.98840999999</v>
       </c>
-      <c r="Q23" s="29">
-        <v>0</v>
-      </c>
-      <c r="R23" s="30">
-        <v>0</v>
-      </c>
-      <c r="S23" s="31">
+      <c r="Q23" s="20">
+        <v>0</v>
+      </c>
+      <c r="R23" s="21">
+        <v>0</v>
+      </c>
+      <c r="S23" s="22">
         <v>14.28017</v>
       </c>
-      <c r="T23" s="31">
+      <c r="T23" s="22">
         <v>0.33800000000000002</v>
       </c>
-      <c r="U23" s="32">
+      <c r="U23" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V23" s="31">
+      <c r="V23" s="22">
         <v>3.5971000000000002E-3</v>
       </c>
-      <c r="W23" s="32">
-        <v>0</v>
-      </c>
-      <c r="X23" s="31">
+      <c r="W23" s="23">
+        <v>0</v>
+      </c>
+      <c r="X23" s="22">
         <v>11.3156374</v>
       </c>
-      <c r="Y23" s="31">
+      <c r="Y23" s="22">
         <v>3.3212465</v>
       </c>
-      <c r="Z23" s="31">
+      <c r="Z23" s="22">
         <v>0.273229</v>
       </c>
-      <c r="AA23" s="31">
+      <c r="AA23" s="22">
         <v>8.5041861999999995</v>
       </c>
-      <c r="AB23" s="31">
+      <c r="AB23" s="22">
         <v>10.034580999999999</v>
       </c>
-      <c r="AC23" s="31">
+      <c r="AC23" s="22">
         <v>0.19036829999999999</v>
       </c>
-      <c r="AD23" s="31">
+      <c r="AD23" s="22">
         <v>9.4305899999999998E-2</v>
       </c>
-      <c r="AE23" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="25">
+      <c r="AE23" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="16">
         <v>7.6414656985000002</v>
       </c>
-      <c r="AG23" s="33">
+      <c r="AG23" s="24">
         <v>186620.80765356499</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" s="19">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A24" s="68">
         <v>46149</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="34">
+      <c r="B24" s="68"/>
+      <c r="C24" s="25">
         <v>355828</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="25">
         <v>33478</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="20">
         <v>139513</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="25">
         <v>22255</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="25">
         <v>4291</v>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="25">
         <v>1935</v>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="25">
         <v>189971</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="25">
         <v>155883</v>
       </c>
-      <c r="K24" s="34">
+      <c r="K24" s="25">
         <v>50896.81</v>
       </c>
-      <c r="L24" s="34">
+      <c r="L24" s="25">
         <v>13182</v>
       </c>
-      <c r="M24" s="34">
+      <c r="M24" s="25">
         <v>77474</v>
       </c>
-      <c r="N24" s="34">
+      <c r="N24" s="25">
         <v>6922</v>
       </c>
-      <c r="O24" s="34">
+      <c r="O24" s="25">
         <v>5222</v>
       </c>
-      <c r="P24" s="28">
+      <c r="P24" s="19">
         <v>139807.01916</v>
       </c>
-      <c r="Q24" s="29">
-        <v>0</v>
-      </c>
-      <c r="R24" s="30">
-        <v>0</v>
-      </c>
-      <c r="S24" s="35">
+      <c r="Q24" s="20">
+        <v>0</v>
+      </c>
+      <c r="R24" s="21">
+        <v>0</v>
+      </c>
+      <c r="S24" s="26">
         <v>17.058923400000001</v>
       </c>
-      <c r="T24" s="35">
+      <c r="T24" s="26">
         <v>0.27800000000000002</v>
       </c>
-      <c r="U24" s="32">
+      <c r="U24" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V24" s="35">
+      <c r="V24" s="26">
         <v>3.6116999999999998E-3</v>
       </c>
-      <c r="W24" s="32">
-        <v>0</v>
-      </c>
-      <c r="X24" s="35">
+      <c r="W24" s="23">
+        <v>0</v>
+      </c>
+      <c r="X24" s="26">
         <v>11.3128329</v>
       </c>
-      <c r="Y24" s="35">
+      <c r="Y24" s="26">
         <v>3.3214448000000001</v>
       </c>
-      <c r="Z24" s="35">
+      <c r="Z24" s="26">
         <v>0.27444299999999999</v>
       </c>
-      <c r="AA24" s="35">
+      <c r="AA24" s="26">
         <v>8.5072443999999994</v>
       </c>
-      <c r="AB24" s="35">
+      <c r="AB24" s="26">
         <v>9.9953310000000002</v>
       </c>
-      <c r="AC24" s="35">
+      <c r="AC24" s="26">
         <v>0.19660059999999999</v>
       </c>
-      <c r="AD24" s="35">
+      <c r="AD24" s="26">
         <v>8.9008500000000004E-2</v>
       </c>
-      <c r="AE24" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="25">
+      <c r="AE24" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="16">
         <v>7.6962986344499997</v>
       </c>
-      <c r="AG24" s="33">
+      <c r="AG24" s="24">
         <v>188216.73757068999</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" s="19">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A25" s="68">
         <v>46150</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="27">
+      <c r="B25" s="68"/>
+      <c r="C25" s="18">
         <v>348494</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="18">
         <v>33642</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="20">
         <v>139513</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="18">
         <v>22230</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="18">
         <v>4335</v>
       </c>
-      <c r="H25" s="27">
+      <c r="H25" s="18">
         <v>1912.3130000000001</v>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="18">
         <v>189396</v>
       </c>
-      <c r="J25" s="27">
+      <c r="J25" s="18">
         <v>157190.29999999999</v>
       </c>
-      <c r="K25" s="27">
+      <c r="K25" s="18">
         <v>50693.85</v>
       </c>
-      <c r="L25" s="27">
+      <c r="L25" s="18">
         <v>12488</v>
       </c>
-      <c r="M25" s="27">
+      <c r="M25" s="18">
         <v>76357</v>
       </c>
-      <c r="N25" s="27">
+      <c r="N25" s="18">
         <v>6914</v>
       </c>
-      <c r="O25" s="27">
+      <c r="O25" s="18">
         <v>5285</v>
       </c>
-      <c r="P25" s="28">
+      <c r="P25" s="19">
         <v>139604.96316000001</v>
       </c>
-      <c r="Q25" s="29">
-        <v>0</v>
-      </c>
-      <c r="R25" s="30">
-        <v>0</v>
-      </c>
-      <c r="S25" s="31">
+      <c r="Q25" s="20">
+        <v>0</v>
+      </c>
+      <c r="R25" s="21">
+        <v>0</v>
+      </c>
+      <c r="S25" s="22">
         <v>14.0980171</v>
       </c>
-      <c r="T25" s="31">
+      <c r="T25" s="22">
         <v>0.27300000000000002</v>
       </c>
-      <c r="U25" s="32">
+      <c r="U25" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V25" s="31">
+      <c r="V25" s="22">
         <v>3.7307E-3</v>
       </c>
-      <c r="W25" s="32">
-        <v>0</v>
-      </c>
-      <c r="X25" s="31">
+      <c r="W25" s="23">
+        <v>0</v>
+      </c>
+      <c r="X25" s="22">
         <v>11.302068</v>
       </c>
-      <c r="Y25" s="31">
+      <c r="Y25" s="22">
         <v>3.3162322999999998</v>
       </c>
-      <c r="Z25" s="31">
+      <c r="Z25" s="22">
         <v>0.272596</v>
       </c>
-      <c r="AA25" s="31">
+      <c r="AA25" s="22">
         <v>8.5108124000000007</v>
       </c>
-      <c r="AB25" s="31">
+      <c r="AB25" s="22">
         <v>10.058695</v>
       </c>
-      <c r="AC25" s="31">
+      <c r="AC25" s="22">
         <v>0.1934844</v>
       </c>
-      <c r="AD25" s="31">
+      <c r="AD25" s="22">
         <v>8.5212499999999997E-2</v>
       </c>
-      <c r="AE25" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF25" s="25">
+      <c r="AE25" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="16">
         <v>7.6191893251750002</v>
       </c>
-      <c r="AG25" s="33">
+      <c r="AG25" s="24">
         <v>187529.66401534999</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A26" s="19">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A26" s="68">
         <v>46151</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="34">
+      <c r="B26" s="68"/>
+      <c r="C26" s="25">
         <v>354258</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="25">
         <v>33704</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="20">
         <v>139513</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="25">
         <v>22202</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="25">
         <v>4404</v>
       </c>
-      <c r="H26" s="34">
+      <c r="H26" s="25">
         <v>1820.201</v>
       </c>
-      <c r="I26" s="34">
+      <c r="I26" s="25">
         <v>190146</v>
       </c>
-      <c r="J26" s="34">
+      <c r="J26" s="25">
         <v>157467.4</v>
       </c>
-      <c r="K26" s="34">
+      <c r="K26" s="25">
         <v>52218.28</v>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="25">
         <v>11192</v>
       </c>
-      <c r="M26" s="34">
+      <c r="M26" s="25">
         <v>77586</v>
       </c>
-      <c r="N26" s="34">
+      <c r="N26" s="25">
         <v>6910</v>
       </c>
-      <c r="O26" s="34">
+      <c r="O26" s="25">
         <v>5339</v>
       </c>
-      <c r="P26" s="28">
+      <c r="P26" s="19">
         <v>140073.90166</v>
       </c>
-      <c r="Q26" s="29">
-        <v>0</v>
-      </c>
-      <c r="R26" s="30">
-        <v>0</v>
-      </c>
-      <c r="S26" s="35">
+      <c r="Q26" s="20">
+        <v>0</v>
+      </c>
+      <c r="R26" s="21">
+        <v>0</v>
+      </c>
+      <c r="S26" s="26">
         <v>14.003682700000001</v>
       </c>
-      <c r="T26" s="35">
+      <c r="T26" s="26">
         <v>0.26400000000000001</v>
       </c>
-      <c r="U26" s="32">
+      <c r="U26" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V26" s="35">
+      <c r="V26" s="26">
         <v>3.7992999999999998E-3</v>
       </c>
-      <c r="W26" s="32">
-        <v>0</v>
-      </c>
-      <c r="X26" s="35">
+      <c r="W26" s="23">
+        <v>0</v>
+      </c>
+      <c r="X26" s="26">
         <v>11.2922096</v>
       </c>
-      <c r="Y26" s="35">
+      <c r="Y26" s="26">
         <v>3.3163173000000001</v>
       </c>
-      <c r="Z26" s="35">
+      <c r="Z26" s="26">
         <v>0.25943100000000002</v>
       </c>
-      <c r="AA26" s="35">
+      <c r="AA26" s="26">
         <v>8.5491817999999995</v>
       </c>
-      <c r="AB26" s="35">
+      <c r="AB26" s="26">
         <v>10.043016</v>
       </c>
-      <c r="AC26" s="35">
+      <c r="AC26" s="26">
         <v>0.1968839</v>
       </c>
-      <c r="AD26" s="35">
+      <c r="AD26" s="26">
         <v>8.6147299999999996E-2</v>
       </c>
-      <c r="AE26" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="25">
+      <c r="AE26" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="16">
         <v>7.603566790975</v>
       </c>
-      <c r="AG26" s="33">
+      <c r="AG26" s="24">
         <v>187900.33677523199</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A27" s="19">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A27" s="68">
         <v>46152</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="27">
+      <c r="B27" s="68"/>
+      <c r="C27" s="18">
         <v>322259</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="18">
         <v>33610</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="20">
         <v>139513</v>
       </c>
-      <c r="F27" s="27">
+      <c r="F27" s="18">
         <v>22097.05</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="18">
         <v>4463</v>
       </c>
-      <c r="H27" s="27">
+      <c r="H27" s="18">
         <v>1943</v>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="18">
         <v>187922</v>
       </c>
-      <c r="J27" s="27">
+      <c r="J27" s="18">
         <v>158085.79999999999</v>
       </c>
-      <c r="K27" s="27">
+      <c r="K27" s="18">
         <v>52467.31</v>
       </c>
-      <c r="L27" s="27">
+      <c r="L27" s="18">
         <v>12427</v>
       </c>
-      <c r="M27" s="27">
+      <c r="M27" s="18">
         <v>81580</v>
       </c>
-      <c r="N27" s="27">
+      <c r="N27" s="18">
         <v>6925</v>
       </c>
-      <c r="O27" s="27">
+      <c r="O27" s="18">
         <v>5370</v>
       </c>
-      <c r="P27" s="28">
+      <c r="P27" s="19">
         <v>139441.38016</v>
       </c>
-      <c r="Q27" s="29">
-        <v>0</v>
-      </c>
-      <c r="R27" s="30">
-        <v>0</v>
-      </c>
-      <c r="S27" s="31">
+      <c r="Q27" s="20">
+        <v>0</v>
+      </c>
+      <c r="R27" s="21">
+        <v>0</v>
+      </c>
+      <c r="S27" s="22">
         <v>16.228895099999999</v>
       </c>
-      <c r="T27" s="31">
+      <c r="T27" s="22">
         <v>0.26500000000000001</v>
       </c>
-      <c r="U27" s="32">
+      <c r="U27" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V27" s="31">
+      <c r="V27" s="22">
         <v>3.6380000000000002E-3</v>
       </c>
-      <c r="W27" s="32">
-        <v>0</v>
-      </c>
-      <c r="X27" s="31">
+      <c r="W27" s="23">
+        <v>0</v>
+      </c>
+      <c r="X27" s="22">
         <v>11.282436300000001</v>
       </c>
-      <c r="Y27" s="31">
+      <c r="Y27" s="22">
         <v>3.3178754000000001</v>
       </c>
-      <c r="Z27" s="31">
+      <c r="Z27" s="22">
         <v>0.27994200000000002</v>
       </c>
-      <c r="AA27" s="31">
+      <c r="AA27" s="22">
         <v>8.5191657999999997</v>
       </c>
-      <c r="AB27" s="31">
+      <c r="AB27" s="22">
         <v>10.096189000000001</v>
       </c>
-      <c r="AC27" s="31">
+      <c r="AC27" s="22">
         <v>0.19546740000000001</v>
       </c>
-      <c r="AD27" s="31">
+      <c r="AD27" s="22">
         <v>8.6798899999999998E-2</v>
       </c>
-      <c r="AE27" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="25">
+      <c r="AE27" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="16">
         <v>7.6958523646749999</v>
       </c>
-      <c r="AG27" s="33">
+      <c r="AG27" s="24">
         <v>187848.29153380499</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" s="19">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A28" s="68">
         <v>46153</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="34">
+      <c r="B28" s="68"/>
+      <c r="C28" s="25">
         <v>343686</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="25">
         <v>33346</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="20">
         <v>139513</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="25">
         <v>22310.39</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="25">
         <v>4405</v>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="25">
         <v>1879.9259999999999</v>
       </c>
-      <c r="I28" s="34">
+      <c r="I28" s="25">
         <v>188597</v>
       </c>
-      <c r="J28" s="34">
+      <c r="J28" s="25">
         <v>156603.20000000001</v>
       </c>
-      <c r="K28" s="34">
+      <c r="K28" s="25">
         <v>48295.01</v>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="25">
         <v>12200</v>
       </c>
-      <c r="M28" s="34">
+      <c r="M28" s="25">
         <v>79883</v>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="25">
         <v>6920</v>
       </c>
-      <c r="O28" s="34">
+      <c r="O28" s="25">
         <v>5375</v>
       </c>
-      <c r="P28" s="28">
+      <c r="P28" s="19">
         <v>138639.35915999999</v>
       </c>
-      <c r="Q28" s="29">
-        <v>0</v>
-      </c>
-      <c r="R28" s="30">
-        <v>0</v>
-      </c>
-      <c r="S28" s="35">
+      <c r="Q28" s="20">
+        <v>0</v>
+      </c>
+      <c r="R28" s="21">
+        <v>0</v>
+      </c>
+      <c r="S28" s="26">
         <v>14.481869700000001</v>
       </c>
-      <c r="T28" s="35">
+      <c r="T28" s="26">
         <v>0.26500000000000001</v>
       </c>
-      <c r="U28" s="32">
+      <c r="U28" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V28" s="35">
+      <c r="V28" s="26">
         <v>2.6941000000000001E-3</v>
       </c>
-      <c r="W28" s="32">
-        <v>0</v>
-      </c>
-      <c r="X28" s="35">
+      <c r="W28" s="23">
+        <v>0</v>
+      </c>
+      <c r="X28" s="26">
         <v>11.289291800000001</v>
       </c>
-      <c r="Y28" s="35">
+      <c r="Y28" s="26">
         <v>3.3171955</v>
       </c>
-      <c r="Z28" s="35">
+      <c r="Z28" s="26">
         <v>0.28168599999999999</v>
       </c>
-      <c r="AA28" s="35">
+      <c r="AA28" s="26">
         <v>8.0337309999999995</v>
       </c>
-      <c r="AB28" s="35">
+      <c r="AB28" s="26">
         <v>10.105112</v>
       </c>
-      <c r="AC28" s="35">
+      <c r="AC28" s="26">
         <v>0.194051</v>
       </c>
-      <c r="AD28" s="35">
+      <c r="AD28" s="26">
         <v>0.11127479999999999</v>
       </c>
-      <c r="AE28" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="25">
+      <c r="AE28" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="16">
         <v>7.5617525697249999</v>
       </c>
-      <c r="AG28" s="33">
+      <c r="AG28" s="24">
         <v>186202.78282357001</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" s="19">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A29" s="68">
         <v>46154</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="27">
+      <c r="B29" s="68"/>
+      <c r="C29" s="18">
         <v>316575</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="18">
         <v>33308</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="20">
         <v>139513</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="18">
         <v>22209.9</v>
       </c>
-      <c r="G29" s="27">
+      <c r="G29" s="18">
         <v>4432</v>
       </c>
-      <c r="H29" s="27">
+      <c r="H29" s="18">
         <v>1887</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="18">
         <v>188969</v>
       </c>
-      <c r="J29" s="27">
+      <c r="J29" s="18">
         <v>158129.9</v>
       </c>
-      <c r="K29" s="27">
+      <c r="K29" s="18">
         <v>51034.36</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="18">
         <v>12090</v>
       </c>
-      <c r="M29" s="27">
+      <c r="M29" s="18">
         <v>82571</v>
       </c>
-      <c r="N29" s="27">
+      <c r="N29" s="18">
         <v>6986</v>
       </c>
-      <c r="O29" s="27">
+      <c r="O29" s="18">
         <v>5539</v>
       </c>
-      <c r="P29" s="28">
+      <c r="P29" s="19">
         <v>139096.35540999999</v>
       </c>
-      <c r="Q29" s="29">
-        <v>0</v>
-      </c>
-      <c r="R29" s="30">
-        <v>0</v>
-      </c>
-      <c r="S29" s="31">
+      <c r="Q29" s="20">
+        <v>0</v>
+      </c>
+      <c r="R29" s="21">
+        <v>0</v>
+      </c>
+      <c r="S29" s="22">
         <v>14.7977337</v>
       </c>
-      <c r="T29" s="31">
+      <c r="T29" s="22">
         <v>0.26800000000000002</v>
       </c>
-      <c r="U29" s="32">
+      <c r="U29" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V29" s="31">
+      <c r="V29" s="22">
         <v>3.4355000000000002E-3</v>
       </c>
-      <c r="W29" s="32">
-        <v>0</v>
-      </c>
-      <c r="X29" s="31">
+      <c r="W29" s="23">
+        <v>0</v>
+      </c>
+      <c r="X29" s="22">
         <v>11.284277599999999</v>
       </c>
-      <c r="Y29" s="31">
+      <c r="Y29" s="22">
         <v>3.3110198</v>
       </c>
-      <c r="Z29" s="31">
+      <c r="Z29" s="22">
         <v>0.25577899999999998</v>
       </c>
-      <c r="AA29" s="31">
+      <c r="AA29" s="22">
         <v>8.5191093000000002</v>
       </c>
-      <c r="AB29" s="31">
+      <c r="AB29" s="22">
         <v>9.9231350000000003</v>
       </c>
-      <c r="AC29" s="31">
+      <c r="AC29" s="22">
         <v>0.19773370000000001</v>
       </c>
-      <c r="AD29" s="31">
+      <c r="AD29" s="22">
         <v>8.96034E-2</v>
       </c>
-      <c r="AE29" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="25">
+      <c r="AE29" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="16">
         <v>7.5860094657249997</v>
       </c>
-      <c r="AG29" s="33">
+      <c r="AG29" s="24">
         <v>186812.35494940999</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" s="19">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A30" s="68">
         <v>46155</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="34">
+      <c r="B30" s="68"/>
+      <c r="C30" s="25">
         <v>321853</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="25">
         <v>28560</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="20">
         <v>139513</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="25">
         <v>22154.19</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="25">
         <v>4502</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="25">
         <v>1854.53</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="25">
         <v>186823</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="25">
         <v>156544.20000000001</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="25">
         <v>50973.94</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="25">
         <v>10908</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="25">
         <v>90614</v>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="25">
         <v>6951</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="25">
         <v>5512</v>
       </c>
-      <c r="P30" s="28">
+      <c r="P30" s="19">
         <v>137097.63540999999</v>
       </c>
-      <c r="Q30" s="29">
-        <v>0</v>
-      </c>
-      <c r="R30" s="30">
-        <v>0</v>
-      </c>
-      <c r="S30" s="35">
+      <c r="Q30" s="20">
+        <v>0</v>
+      </c>
+      <c r="R30" s="21">
+        <v>0</v>
+      </c>
+      <c r="S30" s="26">
         <v>14.047875400000001</v>
       </c>
-      <c r="T30" s="35">
+      <c r="T30" s="26">
         <v>0.253</v>
       </c>
-      <c r="U30" s="32">
+      <c r="U30" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V30" s="35">
+      <c r="V30" s="26">
         <v>3.5014999999999998E-3</v>
       </c>
-      <c r="W30" s="32">
-        <v>0</v>
-      </c>
-      <c r="X30" s="35">
+      <c r="W30" s="23">
+        <v>0</v>
+      </c>
+      <c r="X30" s="26">
         <v>11.2497167</v>
       </c>
-      <c r="Y30" s="35">
+      <c r="Y30" s="26">
         <v>3.3093484000000002</v>
       </c>
-      <c r="Z30" s="35">
+      <c r="Z30" s="26">
         <v>0.26788099999999998</v>
       </c>
-      <c r="AA30" s="35">
+      <c r="AA30" s="26">
         <v>8.5217711000000005</v>
       </c>
-      <c r="AB30" s="35">
+      <c r="AB30" s="26">
         <v>10.071731</v>
       </c>
-      <c r="AC30" s="35">
+      <c r="AC30" s="26">
         <v>0.1957507</v>
       </c>
-      <c r="AD30" s="35">
+      <c r="AD30" s="26">
         <v>8.9008500000000004E-2</v>
       </c>
-      <c r="AE30" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF30" s="25">
+      <c r="AE30" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="16">
         <v>7.60472604945</v>
       </c>
-      <c r="AG30" s="33">
+      <c r="AG30" s="24">
         <v>184931.36226103999</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" s="19">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A31" s="68">
         <v>46156</v>
       </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="27">
+      <c r="B31" s="68"/>
+      <c r="C31" s="18">
         <v>295603</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="18">
         <v>24346</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="20">
         <v>139513</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="18">
         <v>22128.22</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="18">
         <v>4559</v>
       </c>
-      <c r="H31" s="27">
+      <c r="H31" s="18">
         <v>1804.104</v>
       </c>
-      <c r="I31" s="27">
+      <c r="I31" s="18">
         <v>180008</v>
       </c>
-      <c r="J31" s="27">
+      <c r="J31" s="18">
         <v>154691.70000000001</v>
       </c>
-      <c r="K31" s="27">
+      <c r="K31" s="18">
         <v>51204.9</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="18">
         <v>8461</v>
       </c>
-      <c r="M31" s="27">
+      <c r="M31" s="18">
         <v>102944</v>
       </c>
-      <c r="N31" s="27">
+      <c r="N31" s="18">
         <v>7015</v>
       </c>
-      <c r="O31" s="27">
+      <c r="O31" s="18">
         <v>5417</v>
       </c>
-      <c r="P31" s="28">
+      <c r="P31" s="19">
         <v>133236.92916</v>
       </c>
-      <c r="Q31" s="29">
-        <v>0</v>
-      </c>
-      <c r="R31" s="30">
-        <v>0</v>
-      </c>
-      <c r="S31" s="31">
+      <c r="Q31" s="20">
+        <v>0</v>
+      </c>
+      <c r="R31" s="21">
+        <v>0</v>
+      </c>
+      <c r="S31" s="22">
         <v>14.2203965</v>
       </c>
-      <c r="T31" s="31">
+      <c r="T31" s="22">
         <v>0.224</v>
       </c>
-      <c r="U31" s="32">
+      <c r="U31" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V31" s="31">
+      <c r="V31" s="22">
         <v>3.5314000000000001E-3</v>
       </c>
-      <c r="W31" s="32">
-        <v>0</v>
-      </c>
-      <c r="X31" s="31">
+      <c r="W31" s="23">
+        <v>0</v>
+      </c>
+      <c r="X31" s="22">
         <v>11.228696899999999</v>
       </c>
-      <c r="Y31" s="31">
+      <c r="Y31" s="22">
         <v>3.3048441999999998</v>
       </c>
-      <c r="Z31" s="31">
+      <c r="Z31" s="22">
         <v>0.250969</v>
       </c>
-      <c r="AA31" s="31">
+      <c r="AA31" s="22">
         <v>8.4141387999999999</v>
       </c>
-      <c r="AB31" s="31">
+      <c r="AB31" s="22">
         <v>9.9644449999999996</v>
       </c>
-      <c r="AC31" s="31">
+      <c r="AC31" s="22">
         <v>0.1991501</v>
       </c>
-      <c r="AD31" s="31">
+      <c r="AD31" s="22">
         <v>9.1359800000000005E-2</v>
       </c>
-      <c r="AE31" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="25">
+      <c r="AE31" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="16">
         <v>7.532605775625</v>
       </c>
-      <c r="AG31" s="33">
+      <c r="AG31" s="24">
         <v>180617.01948868099</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A32" s="19">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A32" s="68">
         <v>46157</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="34">
+      <c r="B32" s="68"/>
+      <c r="C32" s="25">
         <v>291662</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="25">
         <v>21711</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="20">
         <v>139513</v>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="25">
         <v>22111.77</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="25">
         <v>4582</v>
       </c>
-      <c r="H32" s="34">
+      <c r="H32" s="25">
         <v>1788</v>
       </c>
-      <c r="I32" s="34">
+      <c r="I32" s="25">
         <v>176753</v>
       </c>
-      <c r="J32" s="34">
+      <c r="J32" s="25">
         <v>154995</v>
       </c>
-      <c r="K32" s="34">
+      <c r="K32" s="25">
         <v>52107.15</v>
       </c>
-      <c r="L32" s="34">
+      <c r="L32" s="25">
         <v>10406</v>
       </c>
-      <c r="M32" s="34">
+      <c r="M32" s="25">
         <v>140152</v>
       </c>
-      <c r="N32" s="34">
+      <c r="N32" s="25">
         <v>7015</v>
       </c>
-      <c r="O32" s="34">
+      <c r="O32" s="25">
         <v>5475</v>
       </c>
-      <c r="P32" s="28">
+      <c r="P32" s="19">
         <v>134028.25766</v>
       </c>
-      <c r="Q32" s="29">
-        <v>0</v>
-      </c>
-      <c r="R32" s="30">
-        <v>0</v>
-      </c>
-      <c r="S32" s="35">
+      <c r="Q32" s="20">
+        <v>0</v>
+      </c>
+      <c r="R32" s="21">
+        <v>0</v>
+      </c>
+      <c r="S32" s="26">
         <v>14.298300100000001</v>
       </c>
-      <c r="T32" s="35">
+      <c r="T32" s="26">
         <v>0.19700000000000001</v>
       </c>
-      <c r="U32" s="32">
+      <c r="U32" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V32" s="35">
+      <c r="V32" s="26">
         <v>3.5482999999999999E-3</v>
       </c>
-      <c r="W32" s="32">
-        <v>0</v>
-      </c>
-      <c r="X32" s="35">
+      <c r="W32" s="23">
+        <v>0</v>
+      </c>
+      <c r="X32" s="26">
         <v>11.234447599999999</v>
       </c>
-      <c r="Y32" s="35">
+      <c r="Y32" s="26">
         <v>3.3128044999999999</v>
       </c>
-      <c r="Z32" s="35">
+      <c r="Z32" s="26">
         <v>0.18686800000000001</v>
       </c>
-      <c r="AA32" s="35">
+      <c r="AA32" s="26">
         <v>8.3588079000000004</v>
       </c>
-      <c r="AB32" s="35">
+      <c r="AB32" s="26">
         <v>9.9468999999999994</v>
       </c>
-      <c r="AC32" s="35">
+      <c r="AC32" s="26">
         <v>0.19830030000000001</v>
       </c>
-      <c r="AD32" s="35">
+      <c r="AD32" s="26">
         <v>9.0056700000000003E-2</v>
       </c>
-      <c r="AE32" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="25">
+      <c r="AE32" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="16">
         <v>7.4495935579249997</v>
       </c>
-      <c r="AG32" s="33">
+      <c r="AG32" s="24">
         <v>180886.20113934801</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A33" s="19">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A33" s="68">
         <v>46158</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="27">
+      <c r="B33" s="68"/>
+      <c r="C33" s="18">
         <v>320511</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="18">
         <v>2818</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="20">
         <v>139513</v>
       </c>
-      <c r="F33" s="27">
+      <c r="F33" s="18">
         <v>22076.68</v>
       </c>
-      <c r="G33" s="27">
+      <c r="G33" s="18">
         <v>4629</v>
       </c>
-      <c r="H33" s="27">
+      <c r="H33" s="18">
         <v>1667.348</v>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="18">
         <v>183153</v>
       </c>
-      <c r="J33" s="27">
+      <c r="J33" s="18">
         <v>157204.29999999999</v>
       </c>
-      <c r="K33" s="27">
+      <c r="K33" s="18">
         <v>50685.84</v>
       </c>
-      <c r="L33" s="27">
+      <c r="L33" s="18">
         <v>12840</v>
       </c>
-      <c r="M33" s="27">
+      <c r="M33" s="18">
         <v>181056</v>
       </c>
-      <c r="N33" s="27">
+      <c r="N33" s="18">
         <v>7022</v>
       </c>
-      <c r="O33" s="27">
+      <c r="O33" s="18">
         <v>5459</v>
       </c>
-      <c r="P33" s="28">
+      <c r="P33" s="19">
         <v>133366.08890999999</v>
       </c>
-      <c r="Q33" s="29">
-        <v>0</v>
-      </c>
-      <c r="R33" s="30">
-        <v>0</v>
-      </c>
-      <c r="S33" s="31">
+      <c r="Q33" s="20">
+        <v>0</v>
+      </c>
+      <c r="R33" s="21">
+        <v>0</v>
+      </c>
+      <c r="S33" s="22">
         <v>14.076203899999999</v>
       </c>
-      <c r="T33" s="31">
+      <c r="T33" s="22">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="U33" s="32">
+      <c r="U33" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V33" s="31">
+      <c r="V33" s="22">
         <v>3.2946999999999998E-3</v>
       </c>
-      <c r="W33" s="32">
-        <v>0</v>
-      </c>
-      <c r="X33" s="31">
+      <c r="W33" s="23">
+        <v>0</v>
+      </c>
+      <c r="X33" s="22">
         <v>11.243427799999999</v>
       </c>
-      <c r="Y33" s="31">
+      <c r="Y33" s="22">
         <v>3.3097449999999999</v>
       </c>
-      <c r="Z33" s="31">
+      <c r="Z33" s="22">
         <v>0.12537000000000001</v>
       </c>
-      <c r="AA33" s="31">
+      <c r="AA33" s="22">
         <v>8.3145486999999996</v>
       </c>
-      <c r="AB33" s="31">
+      <c r="AB33" s="22">
         <v>9.8122900000000008</v>
       </c>
-      <c r="AC33" s="31">
+      <c r="AC33" s="22">
         <v>0.19830030000000001</v>
       </c>
-      <c r="AD33" s="31">
+      <c r="AD33" s="22">
         <v>8.9008500000000004E-2</v>
       </c>
-      <c r="AE33" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="25">
+      <c r="AE33" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="16">
         <v>7.3057585230750002</v>
       </c>
-      <c r="AG33" s="33">
+      <c r="AG33" s="24">
         <v>179319.31002014101</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="19">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A34" s="68">
         <v>46159</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="34">
+      <c r="B34" s="68"/>
+      <c r="C34" s="25">
         <v>181679</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="25">
         <v>8604</v>
       </c>
-      <c r="E34" s="29">
+      <c r="E34" s="20">
         <v>139513</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="25">
         <v>22054.86</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="25">
         <v>4662</v>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="25">
         <v>1679</v>
       </c>
-      <c r="I34" s="34">
+      <c r="I34" s="25">
         <v>184635</v>
       </c>
-      <c r="J34" s="34">
+      <c r="J34" s="25">
         <v>154561</v>
       </c>
-      <c r="K34" s="34">
+      <c r="K34" s="25">
         <v>50355.519999999997</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="25">
         <v>15057</v>
       </c>
-      <c r="M34" s="34">
+      <c r="M34" s="25">
         <v>212248</v>
       </c>
-      <c r="N34" s="34">
+      <c r="N34" s="25">
         <v>7004</v>
       </c>
-      <c r="O34" s="34">
+      <c r="O34" s="25">
         <v>5486</v>
       </c>
-      <c r="P34" s="28">
+      <c r="P34" s="19">
         <v>132198.26415999999</v>
       </c>
-      <c r="Q34" s="29">
-        <v>0</v>
-      </c>
-      <c r="R34" s="30">
-        <v>0</v>
-      </c>
-      <c r="S34" s="35">
+      <c r="Q34" s="20">
+        <v>0</v>
+      </c>
+      <c r="R34" s="21">
+        <v>0</v>
+      </c>
+      <c r="S34" s="26">
         <v>8.4637393000000003</v>
       </c>
-      <c r="T34" s="35">
+      <c r="T34" s="26">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="U34" s="32">
+      <c r="U34" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V34" s="35">
+      <c r="V34" s="26">
         <v>3.5103999999999999E-3</v>
       </c>
-      <c r="W34" s="32">
-        <v>0</v>
-      </c>
-      <c r="X34" s="35">
+      <c r="W34" s="23">
+        <v>0</v>
+      </c>
+      <c r="X34" s="26">
         <v>11.217620399999999</v>
       </c>
-      <c r="Y34" s="35">
+      <c r="Y34" s="26">
         <v>3.3135127</v>
       </c>
-      <c r="Z34" s="35">
+      <c r="Z34" s="26">
         <v>0.12257999999999999</v>
       </c>
-      <c r="AA34" s="35">
+      <c r="AA34" s="26">
         <v>8.3427240000000005</v>
       </c>
-      <c r="AB34" s="35">
+      <c r="AB34" s="26">
         <v>9.8826339999999995</v>
       </c>
-      <c r="AC34" s="35">
+      <c r="AC34" s="26">
         <v>0.20169970000000001</v>
       </c>
-      <c r="AD34" s="35">
+      <c r="AD34" s="26">
         <v>8.5127499999999995E-2</v>
       </c>
-      <c r="AE34" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="25">
+      <c r="AE34" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="16">
         <v>7.1530942085250002</v>
       </c>
-      <c r="AG34" s="33">
+      <c r="AG34" s="24">
         <v>177191.22673162201</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="19">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A35" s="68">
         <v>46160</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="27">
+      <c r="B35" s="68"/>
+      <c r="C35" s="18">
         <v>326215</v>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="18">
         <v>11855</v>
       </c>
-      <c r="E35" s="29">
+      <c r="E35" s="20">
         <v>139513</v>
       </c>
-      <c r="F35" s="27">
+      <c r="F35" s="18">
         <v>22068.67</v>
       </c>
-      <c r="G35" s="27">
+      <c r="G35" s="18">
         <v>4682</v>
       </c>
-      <c r="H35" s="27">
+      <c r="H35" s="18">
         <v>1659</v>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="18">
         <v>183112</v>
       </c>
-      <c r="J35" s="27">
+      <c r="J35" s="18">
         <v>155485.79999999999</v>
       </c>
-      <c r="K35" s="27">
+      <c r="K35" s="18">
         <v>53352.93</v>
       </c>
-      <c r="L35" s="27">
+      <c r="L35" s="18">
         <v>14953</v>
       </c>
-      <c r="M35" s="27">
+      <c r="M35" s="18">
         <v>361673</v>
       </c>
-      <c r="N35" s="27">
+      <c r="N35" s="18">
         <v>7013</v>
       </c>
-      <c r="O35" s="27">
+      <c r="O35" s="18">
         <v>5530</v>
       </c>
-      <c r="P35" s="28">
+      <c r="P35" s="19">
         <v>143959.07965999999</v>
       </c>
-      <c r="Q35" s="29">
-        <v>0</v>
-      </c>
-      <c r="R35" s="30">
-        <v>0</v>
-      </c>
-      <c r="S35" s="31">
+      <c r="Q35" s="20">
+        <v>0</v>
+      </c>
+      <c r="R35" s="21">
+        <v>0</v>
+      </c>
+      <c r="S35" s="22">
         <v>12.4810198</v>
       </c>
-      <c r="T35" s="31">
+      <c r="T35" s="22">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="U35" s="32">
+      <c r="U35" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V35" s="31">
+      <c r="V35" s="22">
         <v>3.5596999999999998E-3</v>
       </c>
-      <c r="W35" s="32">
-        <v>0</v>
-      </c>
-      <c r="X35" s="31">
+      <c r="W35" s="23">
+        <v>0</v>
+      </c>
+      <c r="X35" s="22">
         <v>11.208300299999999</v>
       </c>
-      <c r="Y35" s="31">
+      <c r="Y35" s="22">
         <v>3.3142493000000002</v>
       </c>
-      <c r="Z35" s="31">
+      <c r="Z35" s="22">
         <v>0.12049</v>
       </c>
-      <c r="AA35" s="31">
+      <c r="AA35" s="22">
         <v>8.3706443000000004</v>
       </c>
-      <c r="AB35" s="31">
+      <c r="AB35" s="22">
         <v>9.9892909999999997</v>
       </c>
-      <c r="AC35" s="31">
+      <c r="AC35" s="22">
         <v>0.1934844</v>
       </c>
-      <c r="AD35" s="31">
+      <c r="AD35" s="22">
         <v>9.1019799999999998E-2</v>
       </c>
-      <c r="AE35" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="25">
+      <c r="AE35" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="16">
         <v>7.3037430951499998</v>
       </c>
-      <c r="AG35" s="33">
+      <c r="AG35" s="24">
         <v>189899.623728493</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="19">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A36" s="68">
         <v>46161</v>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="34">
+      <c r="B36" s="68"/>
+      <c r="C36" s="25">
         <v>336650</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="25">
         <v>13692</v>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="20">
         <v>139513</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="25">
         <v>22077.919999999998</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="25">
         <v>4707</v>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="25">
         <v>1689</v>
       </c>
-      <c r="I36" s="34">
+      <c r="I36" s="25">
         <v>180576</v>
       </c>
-      <c r="J36" s="34">
+      <c r="J36" s="25">
         <v>152817.5</v>
       </c>
-      <c r="K36" s="34">
+      <c r="K36" s="25">
         <v>51969.85</v>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="25">
         <v>12224</v>
       </c>
-      <c r="M36" s="34">
+      <c r="M36" s="25">
         <v>435555</v>
       </c>
-      <c r="N36" s="34">
+      <c r="N36" s="25">
         <v>7011</v>
       </c>
-      <c r="O36" s="34">
+      <c r="O36" s="25">
         <v>5540</v>
       </c>
-      <c r="P36" s="28">
+      <c r="P36" s="19">
         <v>145563.22915999999</v>
       </c>
-      <c r="Q36" s="29">
-        <v>0</v>
-      </c>
-      <c r="R36" s="30">
-        <v>0</v>
-      </c>
-      <c r="S36" s="35">
+      <c r="Q36" s="20">
+        <v>0</v>
+      </c>
+      <c r="R36" s="21">
+        <v>0</v>
+      </c>
+      <c r="S36" s="26">
         <v>13.4144475</v>
       </c>
-      <c r="T36" s="35">
+      <c r="T36" s="26">
         <v>0.114</v>
       </c>
-      <c r="U36" s="32">
+      <c r="U36" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V36" s="35">
+      <c r="V36" s="26">
         <v>3.6468E-3</v>
       </c>
-      <c r="W36" s="32">
-        <v>0</v>
-      </c>
-      <c r="X36" s="35">
+      <c r="W36" s="23">
+        <v>0</v>
+      </c>
+      <c r="X36" s="26">
         <v>11.199546700000001</v>
       </c>
-      <c r="Y36" s="35">
+      <c r="Y36" s="26">
         <v>3.3056941000000002</v>
       </c>
-      <c r="Z36" s="35">
+      <c r="Z36" s="26">
         <v>0.12488</v>
       </c>
-      <c r="AA36" s="35">
+      <c r="AA36" s="26">
         <v>8.3509639999999994</v>
       </c>
-      <c r="AB36" s="35">
+      <c r="AB36" s="26">
         <v>9.9527929999999998</v>
       </c>
-      <c r="AC36" s="35">
+      <c r="AC36" s="26">
         <v>0.20056660000000001</v>
       </c>
-      <c r="AD36" s="35">
+      <c r="AD36" s="26">
         <v>9.3597700000000006E-2</v>
       </c>
-      <c r="AE36" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="25">
+      <c r="AE36" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="16">
         <v>7.3338989913750003</v>
       </c>
-      <c r="AG36" s="33">
+      <c r="AG36" s="24">
         <v>191693.45381574801</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" s="19">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A37" s="68">
         <v>46162</v>
       </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="27">
+      <c r="B37" s="68"/>
+      <c r="C37" s="18">
         <v>299814</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="18">
         <v>15981</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="20">
         <v>139513</v>
       </c>
-      <c r="F37" s="27">
+      <c r="F37" s="18">
         <v>22045.79</v>
       </c>
-      <c r="G37" s="27">
+      <c r="G37" s="18">
         <v>4337</v>
       </c>
-      <c r="H37" s="27">
+      <c r="H37" s="18">
         <v>1667</v>
       </c>
-      <c r="I37" s="27">
+      <c r="I37" s="18">
         <v>183696</v>
       </c>
-      <c r="J37" s="27">
+      <c r="J37" s="18">
         <v>154073.9</v>
       </c>
-      <c r="K37" s="27">
+      <c r="K37" s="18">
         <v>49012.56</v>
       </c>
-      <c r="L37" s="27">
+      <c r="L37" s="18">
         <v>11826</v>
       </c>
-      <c r="M37" s="27">
+      <c r="M37" s="18">
         <v>451786</v>
       </c>
-      <c r="N37" s="27">
+      <c r="N37" s="18">
         <v>7048</v>
       </c>
-      <c r="O37" s="27">
+      <c r="O37" s="18">
         <v>5591</v>
       </c>
-      <c r="P37" s="28">
+      <c r="P37" s="19">
         <v>145663.34916000001</v>
       </c>
-      <c r="Q37" s="29">
-        <v>0</v>
-      </c>
-      <c r="R37" s="30">
-        <v>0</v>
-      </c>
-      <c r="S37" s="31">
+      <c r="Q37" s="20">
+        <v>0</v>
+      </c>
+      <c r="R37" s="21">
+        <v>0</v>
+      </c>
+      <c r="S37" s="22">
         <v>13.4388103</v>
       </c>
-      <c r="T37" s="31">
+      <c r="T37" s="22">
         <v>0.122</v>
       </c>
-      <c r="U37" s="32">
+      <c r="U37" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V37" s="32">
+      <c r="V37" s="23">
         <v>3.6468E-3</v>
       </c>
-      <c r="W37" s="32">
-        <v>0</v>
-      </c>
-      <c r="X37" s="31">
+      <c r="W37" s="23">
+        <v>0</v>
+      </c>
+      <c r="X37" s="22">
         <v>11.1889235</v>
       </c>
-      <c r="Y37" s="31">
+      <c r="Y37" s="22">
         <v>3.3109915000000001</v>
       </c>
-      <c r="Z37" s="31">
+      <c r="Z37" s="22">
         <v>0.12111</v>
       </c>
-      <c r="AA37" s="31">
+      <c r="AA37" s="22">
         <v>8.4136576000000005</v>
       </c>
-      <c r="AB37" s="31">
+      <c r="AB37" s="22">
         <v>9.9230540000000005</v>
       </c>
-      <c r="AC37" s="31">
+      <c r="AC37" s="22">
         <v>0.20056660000000001</v>
       </c>
-      <c r="AD37" s="31">
+      <c r="AD37" s="22">
         <v>9.3342800000000004E-2</v>
       </c>
-      <c r="AE37" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="25">
+      <c r="AE37" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="16">
         <v>7.3368008372749998</v>
       </c>
-      <c r="AG37" s="33">
+      <c r="AG37" s="24">
         <v>191811.82642645901</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="19">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A38" s="68">
         <v>46163</v>
       </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="34">
+      <c r="B38" s="68"/>
+      <c r="C38" s="25">
         <v>300099</v>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="20">
         <v>15981</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="20">
         <v>139513</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="25">
         <v>21982.33</v>
       </c>
-      <c r="G38" s="29">
+      <c r="G38" s="20">
         <v>4337</v>
       </c>
-      <c r="H38" s="34">
+      <c r="H38" s="25">
         <v>1670</v>
       </c>
-      <c r="I38" s="34">
+      <c r="I38" s="25">
         <v>181734</v>
       </c>
-      <c r="J38" s="34">
+      <c r="J38" s="25">
         <v>150070</v>
       </c>
-      <c r="K38" s="34">
+      <c r="K38" s="25">
         <v>50768.33</v>
       </c>
-      <c r="L38" s="34">
+      <c r="L38" s="25">
         <v>11054</v>
       </c>
-      <c r="M38" s="34">
+      <c r="M38" s="25">
         <v>462052</v>
       </c>
-      <c r="N38" s="34">
+      <c r="N38" s="25">
         <v>7124</v>
       </c>
-      <c r="O38" s="34">
+      <c r="O38" s="25">
         <v>5622</v>
       </c>
-      <c r="P38" s="28">
+      <c r="P38" s="19">
         <v>144880.94691</v>
       </c>
-      <c r="Q38" s="29">
-        <v>0</v>
-      </c>
-      <c r="R38" s="30">
-        <v>0</v>
-      </c>
-      <c r="S38" s="35">
+      <c r="Q38" s="20">
+        <v>0</v>
+      </c>
+      <c r="R38" s="21">
+        <v>0</v>
+      </c>
+      <c r="S38" s="26">
         <v>14.3543909</v>
       </c>
-      <c r="T38" s="32">
+      <c r="T38" s="23">
         <v>0.122</v>
       </c>
-      <c r="U38" s="32">
+      <c r="U38" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V38" s="32">
+      <c r="V38" s="23">
         <v>3.6468E-3</v>
       </c>
-      <c r="W38" s="32">
-        <v>0</v>
-      </c>
-      <c r="X38" s="35">
+      <c r="W38" s="23">
+        <v>0</v>
+      </c>
+      <c r="X38" s="26">
         <v>11.1979603</v>
       </c>
-      <c r="Y38" s="35">
+      <c r="Y38" s="26">
         <v>3.3142209999999999</v>
       </c>
-      <c r="Z38" s="35">
+      <c r="Z38" s="26">
         <v>0.11813</v>
       </c>
-      <c r="AA38" s="35">
+      <c r="AA38" s="26">
         <v>8.4140823000000005</v>
       </c>
-      <c r="AB38" s="35">
+      <c r="AB38" s="26">
         <v>9.9967760000000006</v>
       </c>
-      <c r="AC38" s="35">
+      <c r="AC38" s="26">
         <v>0.1963173</v>
       </c>
-      <c r="AD38" s="35">
+      <c r="AD38" s="26">
         <v>8.9773400000000003E-2</v>
       </c>
-      <c r="AE38" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="25">
+      <c r="AE38" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="16">
         <v>7.3800443178249999</v>
       </c>
-      <c r="AG38" s="33">
+      <c r="AG38" s="24">
         <v>191301.42566911899</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="19">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A39" s="68">
         <v>46164</v>
       </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="29">
+      <c r="B39" s="68"/>
+      <c r="C39" s="20">
         <v>300099</v>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="20">
         <v>15981</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="20">
         <v>139513</v>
       </c>
-      <c r="F39" s="29">
+      <c r="F39" s="20">
         <v>21982.33</v>
       </c>
-      <c r="G39" s="29">
+      <c r="G39" s="20">
         <v>4337</v>
       </c>
-      <c r="H39" s="29">
+      <c r="H39" s="20">
         <v>1670</v>
       </c>
-      <c r="I39" s="29">
+      <c r="I39" s="20">
         <v>181734</v>
       </c>
-      <c r="J39" s="29">
+      <c r="J39" s="20">
         <v>150070</v>
       </c>
-      <c r="K39" s="27">
+      <c r="K39" s="18">
         <v>53275.9</v>
       </c>
-      <c r="L39" s="27">
+      <c r="L39" s="18">
         <v>8080</v>
       </c>
-      <c r="M39" s="29">
+      <c r="M39" s="20">
         <v>462052</v>
       </c>
-      <c r="N39" s="29">
+      <c r="N39" s="20">
         <v>7124</v>
       </c>
-      <c r="O39" s="29">
+      <c r="O39" s="20">
         <v>5622</v>
       </c>
-      <c r="P39" s="28">
+      <c r="P39" s="19">
         <v>144790.36191000001</v>
       </c>
-      <c r="Q39" s="29">
-        <v>0</v>
-      </c>
-      <c r="R39" s="30">
-        <v>0</v>
-      </c>
-      <c r="S39" s="32">
+      <c r="Q39" s="20">
+        <v>0</v>
+      </c>
+      <c r="R39" s="21">
+        <v>0</v>
+      </c>
+      <c r="S39" s="23">
         <v>14.3543909</v>
       </c>
-      <c r="T39" s="32">
+      <c r="T39" s="23">
         <v>0.122</v>
       </c>
-      <c r="U39" s="32">
+      <c r="U39" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V39" s="32">
+      <c r="V39" s="23">
         <v>3.6468E-3</v>
       </c>
-      <c r="W39" s="32">
-        <v>0</v>
-      </c>
-      <c r="X39" s="32">
+      <c r="W39" s="23">
+        <v>0</v>
+      </c>
+      <c r="X39" s="23">
         <v>11.1979603</v>
       </c>
-      <c r="Y39" s="32">
+      <c r="Y39" s="23">
         <v>3.3142209999999999</v>
       </c>
-      <c r="Z39" s="32">
+      <c r="Z39" s="23">
         <v>0.11813</v>
       </c>
-      <c r="AA39" s="32">
+      <c r="AA39" s="23">
         <v>8.4140823000000005</v>
       </c>
-      <c r="AB39" s="32">
+      <c r="AB39" s="23">
         <v>9.9967760000000006</v>
       </c>
-      <c r="AC39" s="32">
+      <c r="AC39" s="23">
         <v>0.1963173</v>
       </c>
-      <c r="AD39" s="32">
+      <c r="AD39" s="23">
         <v>8.9773400000000003E-2</v>
       </c>
-      <c r="AE39" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="25">
+      <c r="AE39" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="16">
         <v>7.3800443178249999</v>
       </c>
-      <c r="AG39" s="33">
+      <c r="AG39" s="24">
         <v>191210.840669119</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A40" s="19">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A40" s="68">
         <v>46165</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="29">
+      <c r="B40" s="68"/>
+      <c r="C40" s="20">
         <v>300099</v>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="20">
         <v>15981</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="20">
         <v>139513</v>
       </c>
-      <c r="F40" s="29">
+      <c r="F40" s="20">
         <v>21982.33</v>
       </c>
-      <c r="G40" s="29">
+      <c r="G40" s="20">
         <v>4337</v>
       </c>
-      <c r="H40" s="29">
+      <c r="H40" s="20">
         <v>1670</v>
       </c>
-      <c r="I40" s="29">
+      <c r="I40" s="20">
         <v>181734</v>
       </c>
-      <c r="J40" s="29">
+      <c r="J40" s="20">
         <v>150070</v>
       </c>
-      <c r="K40" s="34">
+      <c r="K40" s="25">
         <v>56313.23</v>
       </c>
-      <c r="L40" s="34">
+      <c r="L40" s="25">
         <v>13473</v>
       </c>
-      <c r="M40" s="29">
+      <c r="M40" s="20">
         <v>462052</v>
       </c>
-      <c r="N40" s="29">
+      <c r="N40" s="20">
         <v>7124</v>
       </c>
-      <c r="O40" s="29">
+      <c r="O40" s="20">
         <v>5622</v>
       </c>
-      <c r="P40" s="28">
+      <c r="P40" s="19">
         <v>146850.75566</v>
       </c>
-      <c r="Q40" s="29">
-        <v>0</v>
-      </c>
-      <c r="R40" s="30">
-        <v>0</v>
-      </c>
-      <c r="S40" s="32">
+      <c r="Q40" s="20">
+        <v>0</v>
+      </c>
+      <c r="R40" s="21">
+        <v>0</v>
+      </c>
+      <c r="S40" s="23">
         <v>14.3543909</v>
       </c>
-      <c r="T40" s="32">
+      <c r="T40" s="23">
         <v>0.122</v>
       </c>
-      <c r="U40" s="32">
+      <c r="U40" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V40" s="32">
+      <c r="V40" s="23">
         <v>3.6468E-3</v>
       </c>
-      <c r="W40" s="32">
-        <v>0</v>
-      </c>
-      <c r="X40" s="32">
+      <c r="W40" s="23">
+        <v>0</v>
+      </c>
+      <c r="X40" s="23">
         <v>11.1979603</v>
       </c>
-      <c r="Y40" s="32">
+      <c r="Y40" s="23">
         <v>3.3142209999999999</v>
       </c>
-      <c r="Z40" s="32">
+      <c r="Z40" s="23">
         <v>0.11813</v>
       </c>
-      <c r="AA40" s="32">
+      <c r="AA40" s="23">
         <v>8.4140823000000005</v>
       </c>
-      <c r="AB40" s="32">
+      <c r="AB40" s="23">
         <v>9.9967760000000006</v>
       </c>
-      <c r="AC40" s="32">
+      <c r="AC40" s="23">
         <v>0.1963173</v>
       </c>
-      <c r="AD40" s="32">
+      <c r="AD40" s="23">
         <v>8.9773400000000003E-2</v>
       </c>
-      <c r="AE40" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF40" s="25">
+      <c r="AE40" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="16">
         <v>7.3800443178249999</v>
       </c>
-      <c r="AG40" s="33">
+      <c r="AG40" s="24">
         <v>193271.23441911899</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" s="19">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A41" s="68">
         <v>46166</v>
       </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="29">
+      <c r="B41" s="68"/>
+      <c r="C41" s="20">
         <v>300099</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="20">
         <v>15981</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="20">
         <v>139513</v>
       </c>
-      <c r="F41" s="29">
+      <c r="F41" s="20">
         <v>21982.33</v>
       </c>
-      <c r="G41" s="29">
+      <c r="G41" s="20">
         <v>4337</v>
       </c>
-      <c r="H41" s="29">
+      <c r="H41" s="20">
         <v>1670</v>
       </c>
-      <c r="I41" s="29">
+      <c r="I41" s="20">
         <v>181734</v>
       </c>
-      <c r="J41" s="29">
+      <c r="J41" s="20">
         <v>150070</v>
       </c>
-      <c r="K41" s="29">
+      <c r="K41" s="20">
         <v>56313.23</v>
       </c>
-      <c r="L41" s="29">
+      <c r="L41" s="20">
         <v>13473</v>
       </c>
-      <c r="M41" s="29">
+      <c r="M41" s="20">
         <v>462052</v>
       </c>
-      <c r="N41" s="29">
+      <c r="N41" s="20">
         <v>7124</v>
       </c>
-      <c r="O41" s="29">
+      <c r="O41" s="20">
         <v>5622</v>
       </c>
-      <c r="P41" s="28">
+      <c r="P41" s="19">
         <v>146850.75566</v>
       </c>
-      <c r="Q41" s="29">
-        <v>0</v>
-      </c>
-      <c r="R41" s="30">
-        <v>0</v>
-      </c>
-      <c r="S41" s="32">
+      <c r="Q41" s="20">
+        <v>0</v>
+      </c>
+      <c r="R41" s="21">
+        <v>0</v>
+      </c>
+      <c r="S41" s="23">
         <v>14.3543909</v>
       </c>
-      <c r="T41" s="32">
+      <c r="T41" s="23">
         <v>0.122</v>
       </c>
-      <c r="U41" s="32">
+      <c r="U41" s="23">
         <v>1E-3</v>
       </c>
-      <c r="V41" s="32">
+      <c r="V41" s="23">
         <v>3.6468E-3</v>
       </c>
-      <c r="W41" s="32">
-        <v>0</v>
-      </c>
-      <c r="X41" s="32">
+      <c r="W41" s="23">
+        <v>0</v>
+      </c>
+      <c r="X41" s="23">
         <v>11.1979603</v>
       </c>
-      <c r="Y41" s="32">
+      <c r="Y41" s="23">
         <v>3.3142209999999999</v>
       </c>
-      <c r="Z41" s="32">
+      <c r="Z41" s="23">
         <v>0.11813</v>
       </c>
-      <c r="AA41" s="32">
+      <c r="AA41" s="23">
         <v>8.4140823000000005</v>
       </c>
-      <c r="AB41" s="32">
+      <c r="AB41" s="23">
         <v>9.9967760000000006</v>
       </c>
-      <c r="AC41" s="32">
+      <c r="AC41" s="23">
         <v>0.1963173</v>
       </c>
-      <c r="AD41" s="32">
+      <c r="AD41" s="23">
         <v>8.9773400000000003E-2</v>
       </c>
-      <c r="AE41" s="32">
-        <v>0</v>
-      </c>
-      <c r="AF41" s="25">
+      <c r="AE41" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="16">
         <v>7.3800443178249999</v>
       </c>
-      <c r="AG41" s="33">
+      <c r="AG41" s="24">
         <v>193271.23441911899</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="36" t="s">
+    <row r="42" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="36" t="s">
+      <c r="B42" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="37">
+      <c r="C42" s="28">
         <v>414746.54387419298</v>
       </c>
-      <c r="D42" s="37">
+      <c r="D42" s="28">
         <v>23109.916280322501</v>
       </c>
-      <c r="E42" s="37">
+      <c r="E42" s="28">
         <v>92672.413845000003</v>
       </c>
-      <c r="F42" s="37">
+      <c r="F42" s="28">
         <v>22105.990817419301</v>
       </c>
-      <c r="G42" s="37">
+      <c r="G42" s="28">
         <v>5249.0322580645097</v>
       </c>
-      <c r="H42" s="37">
+      <c r="H42" s="28">
         <v>1956.1290322580601</v>
       </c>
-      <c r="I42" s="37">
+      <c r="I42" s="28">
         <v>139574.193548387</v>
       </c>
-      <c r="J42" s="37">
+      <c r="J42" s="28">
         <v>174461.53847999999</v>
       </c>
-      <c r="K42" s="37">
+      <c r="K42" s="28">
         <v>52748.387096774102</v>
       </c>
-      <c r="L42" s="37">
+      <c r="L42" s="28">
         <v>12729.399948386999</v>
       </c>
-      <c r="M42" s="37">
+      <c r="M42" s="28">
         <v>430161.29032258003</v>
       </c>
-      <c r="N42" s="37">
+      <c r="N42" s="28">
         <v>9149.5600258064496</v>
       </c>
-      <c r="O42" s="37">
+      <c r="O42" s="28">
         <v>5298.3870967741896</v>
       </c>
-      <c r="P42" s="37">
+      <c r="P42" s="28">
         <v>145955.32258064501</v>
       </c>
-      <c r="Q42" s="37">
-        <v>0</v>
-      </c>
-      <c r="R42" s="37">
-        <v>0</v>
-      </c>
-      <c r="S42" s="38">
+      <c r="Q42" s="28">
+        <v>0</v>
+      </c>
+      <c r="R42" s="28">
+        <v>0</v>
+      </c>
+      <c r="S42" s="29">
         <v>13.9645300967741</v>
       </c>
-      <c r="T42" s="38">
+      <c r="T42" s="29">
         <v>0.23894861290323</v>
       </c>
-      <c r="U42" s="38">
-        <v>0</v>
-      </c>
-      <c r="V42" s="38">
-        <v>0</v>
-      </c>
-      <c r="W42" s="38">
-        <v>0</v>
-      </c>
-      <c r="X42" s="38">
+      <c r="U42" s="29">
+        <v>0</v>
+      </c>
+      <c r="V42" s="29">
+        <v>0</v>
+      </c>
+      <c r="W42" s="29">
+        <v>0</v>
+      </c>
+      <c r="X42" s="29">
         <v>11.3851992580645</v>
       </c>
-      <c r="Y42" s="38">
+      <c r="Y42" s="29">
         <v>3.2258064516128999</v>
       </c>
-      <c r="Z42" s="38">
+      <c r="Z42" s="29">
         <v>0.25806451612902997</v>
       </c>
-      <c r="AA42" s="38">
+      <c r="AA42" s="29">
         <v>8.5483870967741904</v>
       </c>
-      <c r="AB42" s="38">
+      <c r="AB42" s="29">
         <v>8.4367245483870992</v>
       </c>
-      <c r="AC42" s="38">
+      <c r="AC42" s="29">
         <v>0.29325512903225998</v>
       </c>
-      <c r="AD42" s="38">
+      <c r="AD42" s="29">
         <v>0.24193548387097</v>
       </c>
-      <c r="AE42" s="38">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="38">
+      <c r="AE42" s="29">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="29">
         <v>7.1612903225806503</v>
       </c>
-      <c r="AG42" s="37">
+      <c r="AG42" s="28">
         <v>190999.83870967699</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" s="39" t="s">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A43" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="40">
+      <c r="B43" s="30">
         <v>46143</v>
       </c>
-      <c r="C43" s="41">
+      <c r="C43" s="31">
         <v>315655.29166666599</v>
       </c>
-      <c r="D43" s="41">
+      <c r="D43" s="31">
         <v>25013.375</v>
       </c>
-      <c r="E43" s="41">
+      <c r="E43" s="31">
         <v>139513</v>
       </c>
-      <c r="F43" s="41">
+      <c r="F43" s="31">
         <v>21611.084166666598</v>
       </c>
-      <c r="G43" s="41">
+      <c r="G43" s="31">
         <v>3678.6666666666601</v>
       </c>
-      <c r="H43" s="41">
+      <c r="H43" s="31">
         <v>1806.05925</v>
       </c>
-      <c r="I43" s="41">
+      <c r="I43" s="31">
         <v>185797.66666666599</v>
       </c>
-      <c r="J43" s="41">
+      <c r="J43" s="31">
         <v>154867.870833333</v>
       </c>
-      <c r="K43" s="41">
+      <c r="K43" s="31">
         <v>52345.712500000001</v>
       </c>
-      <c r="L43" s="41">
+      <c r="L43" s="31">
         <v>12245.5</v>
       </c>
-      <c r="M43" s="41">
+      <c r="M43" s="31">
         <v>254327.83333333299</v>
       </c>
-      <c r="N43" s="41">
+      <c r="N43" s="31">
         <v>6982.4166666666597</v>
       </c>
-      <c r="O43" s="41">
+      <c r="O43" s="31">
         <v>5409.9166666666597</v>
       </c>
-      <c r="P43" s="41">
+      <c r="P43" s="31">
         <v>141654.33077458301</v>
       </c>
-      <c r="Q43" s="41">
-        <v>0</v>
-      </c>
-      <c r="R43" s="41">
-        <v>0</v>
-      </c>
-      <c r="S43" s="42">
+      <c r="Q43" s="31">
+        <v>0</v>
+      </c>
+      <c r="R43" s="31">
+        <v>0</v>
+      </c>
+      <c r="S43" s="32">
         <v>14.0753894916666</v>
       </c>
-      <c r="T43" s="42">
+      <c r="T43" s="32">
         <v>0.24941666666667001</v>
       </c>
-      <c r="U43" s="42">
+      <c r="U43" s="32">
         <v>1E-3</v>
       </c>
-      <c r="V43" s="42">
+      <c r="V43" s="32">
         <v>3.4548249999999999E-3</v>
       </c>
-      <c r="W43" s="42">
-        <v>0</v>
-      </c>
-      <c r="X43" s="42">
+      <c r="W43" s="32">
+        <v>0</v>
+      </c>
+      <c r="X43" s="32">
         <v>11.260911233333299</v>
       </c>
-      <c r="Y43" s="42">
+      <c r="Y43" s="32">
         <v>3.3151369291666701</v>
       </c>
-      <c r="Z43" s="42">
+      <c r="Z43" s="32">
         <v>0.21150687500000001</v>
       </c>
-      <c r="AA43" s="42">
+      <c r="AA43" s="32">
         <v>8.4406965125000006</v>
       </c>
-      <c r="AB43" s="42">
+      <c r="AB43" s="32">
         <v>9.9899538333333293</v>
       </c>
-      <c r="AC43" s="42">
+      <c r="AC43" s="32">
         <v>0.19663598333332999</v>
       </c>
-      <c r="AD43" s="42">
+      <c r="AD43" s="32">
         <v>9.1028104166669996E-2</v>
       </c>
-      <c r="AE43" s="42">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="42">
+      <c r="AE43" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="32">
         <v>7.5144719017562496</v>
       </c>
-      <c r="AG43" s="41">
+      <c r="AG43" s="31">
         <v>188920.35903662999</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="39"/>
-      <c r="B44" s="40">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A44" s="69"/>
+      <c r="B44" s="30">
         <v>45778</v>
       </c>
-      <c r="C44" s="41">
+      <c r="C44" s="31">
         <v>322606.625</v>
       </c>
-      <c r="D44" s="41">
+      <c r="D44" s="31">
         <v>28012.152083333302</v>
       </c>
-      <c r="E44" s="41">
-        <v>0</v>
-      </c>
-      <c r="F44" s="41">
+      <c r="E44" s="31">
+        <v>0</v>
+      </c>
+      <c r="F44" s="31">
         <v>18284.208333333299</v>
       </c>
-      <c r="G44" s="41">
+      <c r="G44" s="31">
         <v>4761.9583333333303</v>
       </c>
-      <c r="H44" s="41">
+      <c r="H44" s="31">
         <v>2143.5271666666599</v>
       </c>
-      <c r="I44" s="41">
-        <v>0</v>
-      </c>
-      <c r="J44" s="41">
+      <c r="I44" s="31">
+        <v>0</v>
+      </c>
+      <c r="J44" s="31">
         <v>168970.6</v>
       </c>
-      <c r="K44" s="41">
+      <c r="K44" s="31">
         <v>52278.690416666599</v>
       </c>
-      <c r="L44" s="41">
+      <c r="L44" s="31">
         <v>10549.666666666601</v>
       </c>
-      <c r="M44" s="41">
+      <c r="M44" s="31">
         <v>409877.25</v>
       </c>
-      <c r="N44" s="41">
+      <c r="N44" s="31">
         <v>7347.5</v>
       </c>
-      <c r="O44" s="41">
+      <c r="O44" s="31">
         <v>4532.7916666666597</v>
       </c>
-      <c r="P44" s="41">
+      <c r="P44" s="31">
         <v>112886.54436458299</v>
       </c>
-      <c r="Q44" s="41">
+      <c r="Q44" s="31">
         <v>131.75833333333301</v>
       </c>
-      <c r="R44" s="41">
+      <c r="R44" s="31">
         <v>59.291249999999998</v>
       </c>
-      <c r="S44" s="42">
+      <c r="S44" s="32">
         <v>9.3689211583333307</v>
       </c>
-      <c r="T44" s="42">
+      <c r="T44" s="32">
         <v>0.33866666666667</v>
       </c>
-      <c r="U44" s="42">
-        <v>0</v>
-      </c>
-      <c r="V44" s="42">
+      <c r="U44" s="32">
+        <v>0</v>
+      </c>
+      <c r="V44" s="32">
         <v>2.8779166666699999E-3</v>
       </c>
-      <c r="W44" s="42">
-        <v>0</v>
-      </c>
-      <c r="X44" s="42">
+      <c r="W44" s="32">
+        <v>0</v>
+      </c>
+      <c r="X44" s="32">
         <v>10.1131137875</v>
       </c>
-      <c r="Y44" s="42">
+      <c r="Y44" s="32">
         <v>3.7156633666666701</v>
       </c>
-      <c r="Z44" s="42">
+      <c r="Z44" s="32">
         <v>0.25355862499999998</v>
       </c>
-      <c r="AA44" s="42">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="42">
+      <c r="AA44" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="32">
         <v>10.7036902916666</v>
       </c>
-      <c r="AC44" s="42">
+      <c r="AC44" s="32">
         <v>0.19035646666667</v>
       </c>
-      <c r="AD44" s="42">
+      <c r="AD44" s="32">
         <v>6.9793441666669995E-2</v>
       </c>
-      <c r="AE44" s="42">
+      <c r="AE44" s="32">
         <v>0.31570833333332998</v>
       </c>
-      <c r="AF44" s="42">
+      <c r="AF44" s="32">
         <v>5.9458310405895798</v>
       </c>
-      <c r="AG44" s="41">
+      <c r="AG44" s="31">
         <v>150345.112859891</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" s="43" t="s">
+    <row r="45" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="44">
+      <c r="B45" s="33">
         <v>46113</v>
       </c>
-      <c r="C45" s="45">
+      <c r="C45" s="34">
         <v>321916.63333333301</v>
       </c>
-      <c r="D45" s="45">
+      <c r="D45" s="34">
         <v>34817.304333333297</v>
       </c>
-      <c r="E45" s="45">
+      <c r="E45" s="34">
         <v>139513</v>
       </c>
-      <c r="F45" s="45">
+      <c r="F45" s="34">
         <v>18331.464666666601</v>
       </c>
-      <c r="G45" s="45">
+      <c r="G45" s="34">
         <v>4478.7333333333299</v>
       </c>
-      <c r="H45" s="45">
+      <c r="H45" s="34">
         <v>1968.8087666666599</v>
       </c>
-      <c r="I45" s="45">
+      <c r="I45" s="34">
         <v>189203.96666666601</v>
       </c>
-      <c r="J45" s="45">
+      <c r="J45" s="34">
         <v>155715.78333333301</v>
       </c>
-      <c r="K45" s="45">
+      <c r="K45" s="34">
         <v>53739.09</v>
       </c>
-      <c r="L45" s="45">
+      <c r="L45" s="34">
         <v>13140.766666666599</v>
       </c>
-      <c r="M45" s="45">
+      <c r="M45" s="34">
         <v>241264.6</v>
       </c>
-      <c r="N45" s="45">
+      <c r="N45" s="34">
         <v>7012.1666666666597</v>
       </c>
-      <c r="O45" s="45">
+      <c r="O45" s="34">
         <v>4271.0333333333301</v>
       </c>
-      <c r="P45" s="45">
+      <c r="P45" s="34">
         <v>143242.81967999999</v>
       </c>
-      <c r="Q45" s="45">
-        <v>0</v>
-      </c>
-      <c r="R45" s="45">
-        <v>0</v>
-      </c>
-      <c r="S45" s="46">
+      <c r="Q45" s="34">
+        <v>0</v>
+      </c>
+      <c r="R45" s="34">
+        <v>0</v>
+      </c>
+      <c r="S45" s="35">
         <v>14.5437771233333</v>
       </c>
-      <c r="T45" s="46">
+      <c r="T45" s="35">
         <v>0.45336666666667003</v>
       </c>
-      <c r="U45" s="46">
+      <c r="U45" s="35">
         <v>4.0666000000000002</v>
       </c>
-      <c r="V45" s="46">
+      <c r="V45" s="35">
         <v>2.9620766666700001E-3</v>
       </c>
-      <c r="W45" s="46">
-        <v>0</v>
-      </c>
-      <c r="X45" s="46">
+      <c r="W45" s="35">
+        <v>0</v>
+      </c>
+      <c r="X45" s="35">
         <v>10.2261322066666</v>
       </c>
-      <c r="Y45" s="46">
+      <c r="Y45" s="35">
         <v>2.9671992500000002</v>
       </c>
-      <c r="Z45" s="46">
+      <c r="Z45" s="35">
         <v>0.27878036666667</v>
       </c>
-      <c r="AA45" s="46">
+      <c r="AA45" s="35">
         <v>9.7019340433333294</v>
       </c>
-      <c r="AB45" s="46">
+      <c r="AB45" s="35">
         <v>9.9742985999999991</v>
       </c>
-      <c r="AC45" s="46">
+      <c r="AC45" s="35">
         <v>0.20279508333332999</v>
       </c>
-      <c r="AD45" s="46">
+      <c r="AD45" s="35">
         <v>8.9445693333329995E-2</v>
       </c>
-      <c r="AE45" s="46">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="46">
+      <c r="AE45" s="35">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="35">
         <v>7.6727593419908304</v>
       </c>
-      <c r="AG45" s="45">
+      <c r="AG45" s="34">
         <v>191504.47594112199</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="47" t="s">
+    <row r="46" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="47" t="s">
+      <c r="B46" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="C46" s="48">
+      <c r="C46" s="37">
         <v>414774.95108424599</v>
       </c>
-      <c r="D46" s="48">
+      <c r="D46" s="37">
         <v>23688.482943315001</v>
       </c>
-      <c r="E46" s="48">
+      <c r="E46" s="37">
         <v>110191.308517068</v>
       </c>
-      <c r="F46" s="48">
+      <c r="F46" s="37">
         <v>22241.0959308493</v>
       </c>
-      <c r="G46" s="48">
+      <c r="G46" s="37">
         <v>5461.1506849315001</v>
       </c>
-      <c r="H46" s="48">
+      <c r="H46" s="37">
         <v>2097.4794520547898</v>
       </c>
-      <c r="I46" s="48">
+      <c r="I46" s="37">
         <v>139900.54794520501</v>
       </c>
-      <c r="J46" s="48">
+      <c r="J46" s="37">
         <v>174593.04534377999</v>
       </c>
-      <c r="K46" s="48">
+      <c r="K46" s="37">
         <v>52400</v>
       </c>
-      <c r="L46" s="48">
+      <c r="L46" s="37">
         <v>13127.972168767101</v>
       </c>
-      <c r="M46" s="48">
+      <c r="M46" s="37">
         <v>431104.10958904098</v>
       </c>
-      <c r="N46" s="48">
+      <c r="N46" s="37">
         <v>7770.8591999999999</v>
       </c>
-      <c r="O46" s="48">
+      <c r="O46" s="37">
         <v>5220</v>
       </c>
-      <c r="P46" s="74">
+      <c r="P46" s="78">
         <v>146458.04109588999</v>
       </c>
-      <c r="Q46" s="48"/>
-      <c r="R46" s="48"/>
-      <c r="S46" s="49">
+      <c r="Q46" s="37"/>
+      <c r="R46" s="37"/>
+      <c r="S46" s="38">
         <v>13.757931569863</v>
       </c>
-      <c r="T46" s="49">
+      <c r="T46" s="38">
         <v>0.25367832328766998</v>
       </c>
-      <c r="U46" s="49">
+      <c r="U46" s="38">
         <v>4.7236655671232901</v>
       </c>
-      <c r="V46" s="49">
+      <c r="V46" s="38">
         <v>3.9138931506799996E-3</v>
       </c>
-      <c r="W46" s="49">
+      <c r="W46" s="38">
         <v>2.1917808219180001E-2</v>
       </c>
-      <c r="X46" s="49">
+      <c r="X46" s="38">
         <v>10.829975827397201</v>
       </c>
-      <c r="Y46" s="49">
+      <c r="Y46" s="38">
         <v>3.2554391616438401</v>
       </c>
-      <c r="Z46" s="49">
+      <c r="Z46" s="38">
         <v>0.25753424657534002</v>
       </c>
-      <c r="AA46" s="49">
+      <c r="AA46" s="38">
         <v>8.4794520547945194</v>
       </c>
-      <c r="AB46" s="49">
+      <c r="AB46" s="38">
         <v>8.4299262301369904</v>
       </c>
-      <c r="AC46" s="49">
+      <c r="AC46" s="38">
         <v>0.22415940000000001</v>
       </c>
-      <c r="AD46" s="49">
+      <c r="AD46" s="38">
         <v>0.21917808219178</v>
       </c>
-      <c r="AE46" s="49"/>
-      <c r="AF46" s="74">
+      <c r="AE46" s="38"/>
+      <c r="AF46" s="60">
         <v>7.0630136986301402</v>
       </c>
-      <c r="AG46" s="78">
+      <c r="AG46" s="63">
         <v>190884.39726027299</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A47" s="50" t="s">
+    <row r="47" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="50" t="s">
+      <c r="B47" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="51">
+      <c r="C47" s="40">
         <v>416474.65474999999</v>
       </c>
-      <c r="D47" s="51">
+      <c r="D47" s="40">
         <v>23537.8777487037</v>
       </c>
-      <c r="E47" s="51">
+      <c r="E47" s="40">
         <v>94388.593617499995</v>
       </c>
-      <c r="F47" s="51">
+      <c r="F47" s="40">
         <v>22124.884803333302</v>
       </c>
-      <c r="G47" s="51">
+      <c r="G47" s="40">
         <v>5346.2366644444401</v>
       </c>
-      <c r="H47" s="51">
+      <c r="H47" s="40">
         <v>1992.35358962962</v>
       </c>
-      <c r="I47" s="51">
+      <c r="I47" s="40">
         <v>140086.678881481</v>
       </c>
-      <c r="J47" s="51">
+      <c r="J47" s="40">
         <v>174512.82076444401</v>
       </c>
-      <c r="K47" s="51">
+      <c r="K47" s="40">
         <v>52643.727755555497</v>
       </c>
-      <c r="L47" s="51">
+      <c r="L47" s="40">
         <v>12965.1297111111</v>
       </c>
-      <c r="M47" s="51">
+      <c r="M47" s="40">
         <v>431071.68322222203</v>
       </c>
-      <c r="N47" s="51">
+      <c r="N47" s="40">
         <v>8268.4915733333291</v>
       </c>
-      <c r="O47" s="51">
+      <c r="O47" s="40">
         <v>5092.3386233333304</v>
       </c>
-      <c r="P47" s="74">
+      <c r="P47" s="60">
         <v>146216.439887407</v>
       </c>
-      <c r="Q47" s="51">
-        <v>0</v>
-      </c>
-      <c r="R47" s="51">
-        <v>0</v>
-      </c>
-      <c r="S47" s="52">
+      <c r="Q47" s="40">
+        <v>0</v>
+      </c>
+      <c r="R47" s="40">
+        <v>0</v>
+      </c>
+      <c r="S47" s="41">
         <v>14.2231321111111</v>
       </c>
-      <c r="T47" s="52">
+      <c r="T47" s="41">
         <v>0.24337359259259</v>
       </c>
-      <c r="U47" s="52">
+      <c r="U47" s="41">
         <v>7.9821200555555603</v>
       </c>
-      <c r="V47" s="52">
+      <c r="V47" s="41">
         <v>2.6455018518520002E-2</v>
       </c>
-      <c r="W47" s="52">
+      <c r="W47" s="41">
         <v>3.7037037037039998E-2</v>
       </c>
-      <c r="X47" s="52">
+      <c r="X47" s="41">
         <v>11.596036259259201</v>
       </c>
-      <c r="Y47" s="52">
+      <c r="Y47" s="41">
         <v>3.3944760370370402</v>
       </c>
-      <c r="Z47" s="52">
+      <c r="Z47" s="41">
         <v>0.26284348148148001</v>
       </c>
-      <c r="AA47" s="52">
+      <c r="AA47" s="41">
         <v>8.5215053703703703</v>
       </c>
-      <c r="AB47" s="52">
+      <c r="AB47" s="41">
         <v>8.4505100370370396</v>
       </c>
-      <c r="AC47" s="52">
+      <c r="AC47" s="41">
         <v>0.29868585185184998</v>
       </c>
-      <c r="AD47" s="52">
+      <c r="AD47" s="41">
         <v>0.20011950000000001</v>
       </c>
-      <c r="AE47" s="52">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="74">
+      <c r="AE47" s="41">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="60">
         <v>7.2753882777777799</v>
       </c>
-      <c r="AG47" s="78">
+      <c r="AG47" s="63">
         <v>191978.63215462901</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="53" t="s">
+    <row r="48" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="54" t="s">
+      <c r="B48" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="C48" s="55">
+      <c r="C48" s="43">
         <v>319133.81481481402</v>
       </c>
-      <c r="D48" s="55">
+      <c r="D48" s="43">
         <v>30864.712962964801</v>
       </c>
-      <c r="E48" s="55">
+      <c r="E48" s="43">
         <v>137407.04888888801</v>
       </c>
-      <c r="F48" s="55">
+      <c r="F48" s="43">
         <v>19755.2040740759</v>
       </c>
-      <c r="G48" s="55">
+      <c r="G48" s="43">
         <v>4125.2777777814799</v>
       </c>
-      <c r="H48" s="55">
+      <c r="H48" s="43">
         <v>1895.5633703573999</v>
       </c>
-      <c r="I48" s="55">
+      <c r="I48" s="43">
         <v>187690.05555555501</v>
       </c>
-      <c r="J48" s="55">
+      <c r="J48" s="43">
         <v>155315.23388888501</v>
       </c>
-      <c r="K48" s="55">
+      <c r="K48" s="43">
         <v>53115.112962961102</v>
       </c>
-      <c r="L48" s="55">
+      <c r="L48" s="43">
         <v>12742.8518518537</v>
       </c>
-      <c r="M48" s="55">
+      <c r="M48" s="43">
         <v>246667.38888889001</v>
       </c>
-      <c r="N48" s="55">
+      <c r="N48" s="43">
         <v>7005.0185185148102</v>
       </c>
-      <c r="O48" s="55">
+      <c r="O48" s="43">
         <v>4809.9629629648098</v>
       </c>
-      <c r="P48" s="55">
+      <c r="P48" s="79">
         <v>142607.96199787699</v>
       </c>
-      <c r="Q48" s="55">
-        <v>0</v>
-      </c>
-      <c r="R48" s="55">
-        <v>0</v>
-      </c>
-      <c r="S48" s="56">
+      <c r="Q48" s="43">
+        <v>0</v>
+      </c>
+      <c r="R48" s="43">
+        <v>0</v>
+      </c>
+      <c r="S48" s="44">
         <v>6.2570038440246103</v>
       </c>
-      <c r="T48" s="56">
+      <c r="T48" s="44">
         <v>0.11085185185184999</v>
       </c>
-      <c r="U48" s="56">
+      <c r="U48" s="44">
         <v>4.4444444444E-4</v>
       </c>
-      <c r="V48" s="56">
+      <c r="V48" s="44">
         <v>1.5357398036299999E-3</v>
       </c>
-      <c r="W48" s="56">
+      <c r="W48" s="44">
         <v>2.4789524799999999E-6</v>
       </c>
-      <c r="X48" s="56">
+      <c r="X48" s="44">
         <v>5.0057526460289701</v>
       </c>
-      <c r="Y48" s="56">
+      <c r="Y48" s="44">
         <v>1.47365626451304</v>
       </c>
-      <c r="Z48" s="56">
+      <c r="Z48" s="44">
         <v>9.4027668402810002E-2</v>
       </c>
-      <c r="AA48" s="56">
+      <c r="AA48" s="44">
         <v>3.7522775673538198</v>
       </c>
-      <c r="AB48" s="56">
+      <c r="AB48" s="44">
         <v>4.4408603504101203</v>
       </c>
-      <c r="AC48" s="56">
+      <c r="AC48" s="44">
         <v>8.7411651941650001E-2</v>
       </c>
-      <c r="AD48" s="56">
+      <c r="AD48" s="44">
         <v>4.0465222926749998E-2</v>
       </c>
-      <c r="AE48" s="56">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="56">
+      <c r="AE48" s="44">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="44">
         <v>3.3404324095481499</v>
       </c>
-      <c r="AG48" s="55">
+      <c r="AG48" s="43">
         <v>163619.28185393501</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" s="53"/>
-      <c r="B49" s="54" t="s">
+    <row r="49" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="70"/>
+      <c r="B49" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="C49" s="55">
+      <c r="C49" s="43">
         <v>323980.03197213297</v>
       </c>
-      <c r="D49" s="55">
+      <c r="D49" s="43">
         <v>27093.432738281401</v>
       </c>
-      <c r="E49" s="55">
-        <v>0</v>
-      </c>
-      <c r="F49" s="55">
+      <c r="E49" s="43">
+        <v>0</v>
+      </c>
+      <c r="F49" s="43">
         <v>21968.771348859202</v>
       </c>
-      <c r="G49" s="55">
+      <c r="G49" s="43">
         <v>4855.3518518518504</v>
       </c>
-      <c r="H49" s="55">
+      <c r="H49" s="43">
         <v>2099.5368010407401</v>
       </c>
-      <c r="I49" s="55">
+      <c r="I49" s="43">
         <v>146606.94145758299</v>
       </c>
-      <c r="J49" s="55">
+      <c r="J49" s="43">
         <v>169336.204552468</v>
       </c>
-      <c r="K49" s="55">
+      <c r="K49" s="43">
         <v>50425.1513802111</v>
       </c>
-      <c r="L49" s="55">
+      <c r="L49" s="43">
         <v>10555.9695583388</v>
       </c>
-      <c r="M49" s="55">
+      <c r="M49" s="43">
         <v>361171.89452508802</v>
       </c>
-      <c r="N49" s="55">
+      <c r="N49" s="43">
         <v>7255.3518518518504</v>
       </c>
-      <c r="O49" s="55">
+      <c r="O49" s="43">
         <v>4406.50990373888</v>
       </c>
-      <c r="P49" s="55">
+      <c r="P49" s="43">
         <v>142206.280868081</v>
       </c>
-      <c r="Q49" s="55">
+      <c r="Q49" s="43">
         <v>131.56629629814799</v>
       </c>
-      <c r="R49" s="55">
+      <c r="R49" s="43">
         <v>59.204833340740699</v>
       </c>
-      <c r="S49" s="56">
+      <c r="S49" s="44">
         <v>1.5909257298500001E-3</v>
       </c>
-      <c r="T49" s="56">
+      <c r="T49" s="44">
         <v>5.137357505E-5</v>
       </c>
-      <c r="U49" s="56">
-        <v>0</v>
-      </c>
-      <c r="V49" s="56">
+      <c r="U49" s="44">
+        <v>0</v>
+      </c>
+      <c r="V49" s="44">
         <v>5.6150032000000004E-7</v>
       </c>
-      <c r="W49" s="56">
+      <c r="W49" s="44">
         <v>4.3446670200000003E-6</v>
       </c>
-      <c r="X49" s="56">
+      <c r="X49" s="44">
         <v>1.5692534737700001E-3</v>
       </c>
-      <c r="Y49" s="56">
+      <c r="Y49" s="44">
         <v>5.9452546664000001E-4</v>
       </c>
-      <c r="Z49" s="56">
+      <c r="Z49" s="44">
         <v>4.2818749339999999E-5</v>
       </c>
-      <c r="AA49" s="56">
+      <c r="AA49" s="44">
         <v>1.3870226956399999E-3</v>
       </c>
-      <c r="AB49" s="56">
+      <c r="AB49" s="44">
         <v>1.6505633724900001E-3</v>
       </c>
-      <c r="AC49" s="56">
+      <c r="AC49" s="44">
         <v>3.0262825470000001E-5</v>
       </c>
-      <c r="AD49" s="56">
+      <c r="AD49" s="44">
         <v>1.8067396509999999E-5</v>
       </c>
-      <c r="AE49" s="56">
+      <c r="AE49" s="44">
         <v>7.0094779489999996E-5</v>
       </c>
-      <c r="AF49" s="56">
+      <c r="AF49" s="44">
         <v>1.2222815368299999E-3</v>
       </c>
-      <c r="AG49" s="55">
+      <c r="AG49" s="43">
         <v>142273.17385228799</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" s="57" t="s">
+    <row r="50" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="B50" s="57" t="s">
+      <c r="B50" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="C50" s="58">
+      <c r="C50" s="46">
         <v>431381.45062942099</v>
       </c>
-      <c r="D50" s="58">
+      <c r="D50" s="46">
         <v>22442.449435080001</v>
       </c>
-      <c r="E50" s="58">
+      <c r="E50" s="46">
         <v>105465.745880161</v>
       </c>
-      <c r="F50" s="58">
+      <c r="F50" s="46">
         <v>22672.729886688001</v>
       </c>
-      <c r="G50" s="58">
+      <c r="G50" s="46">
         <v>5693.1028938899999</v>
       </c>
-      <c r="H50" s="58">
+      <c r="H50" s="46">
         <v>2132.538836015</v>
       </c>
-      <c r="I50" s="58">
+      <c r="I50" s="46">
         <v>131602.691318328</v>
       </c>
-      <c r="J50" s="58">
+      <c r="J50" s="46">
         <v>177940.31807228399</v>
       </c>
-      <c r="K50" s="58">
+      <c r="K50" s="46">
         <v>52275.832475884999</v>
       </c>
-      <c r="L50" s="58">
+      <c r="L50" s="46">
         <v>13194.841934405</v>
       </c>
-      <c r="M50" s="58">
+      <c r="M50" s="46">
         <v>463128.49196141399</v>
       </c>
-      <c r="N50" s="58">
+      <c r="N50" s="46">
         <v>7903.8347524119999</v>
       </c>
-      <c r="O50" s="58">
+      <c r="O50" s="46">
         <v>5291.1961414790003</v>
       </c>
-      <c r="P50" s="58">
+      <c r="P50" s="46">
         <v>147126.54357593099</v>
       </c>
-      <c r="Q50" s="58" t="s">
+      <c r="Q50" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="R50" s="58" t="s">
+      <c r="R50" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="S50" s="59">
+      <c r="S50" s="47">
         <v>15.060343458</v>
       </c>
-      <c r="T50" s="59">
+      <c r="T50" s="47">
         <v>0.27847777499999998</v>
       </c>
-      <c r="U50" s="59">
+      <c r="U50" s="47">
         <v>5.5437747010000002</v>
       </c>
-      <c r="V50" s="59">
+      <c r="V50" s="47">
         <v>4.3268200000000003E-3</v>
       </c>
-      <c r="W50" s="59">
+      <c r="W50" s="47">
         <v>2.5723042000000002E-2</v>
       </c>
-      <c r="X50" s="59">
+      <c r="X50" s="47">
         <v>11.841255736999999</v>
       </c>
-      <c r="Y50" s="59">
+      <c r="Y50" s="47">
         <v>3.5648162559999998</v>
       </c>
-      <c r="Z50" s="59">
+      <c r="Z50" s="47">
         <v>0.28592445599999999</v>
       </c>
-      <c r="AA50" s="59">
+      <c r="AA50" s="47">
         <v>9.3002476250000008</v>
       </c>
-      <c r="AB50" s="59">
+      <c r="AB50" s="47">
         <v>9.1225614630000003</v>
       </c>
-      <c r="AC50" s="59">
+      <c r="AC50" s="47">
         <v>0.24790338200000001</v>
       </c>
-      <c r="AD50" s="59">
+      <c r="AD50" s="47">
         <v>0.25020861100000003</v>
       </c>
-      <c r="AE50" s="59" t="s">
+      <c r="AE50" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="AF50" s="59">
+      <c r="AF50" s="47">
         <v>7.7093782949999996</v>
       </c>
-      <c r="AG50" s="58">
+      <c r="AG50" s="46">
         <v>195618.53305430099</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" s="60" t="s">
+    <row r="51" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="60"/>
-      <c r="C51" s="61">
+      <c r="B51" s="48"/>
+      <c r="C51" s="49">
         <v>328625.63561643503</v>
       </c>
-      <c r="D51" s="61">
+      <c r="D51" s="49">
         <v>23919.8843479432</v>
       </c>
-      <c r="E51" s="61">
+      <c r="E51" s="49">
         <v>106999.63991769501</v>
       </c>
-      <c r="F51" s="61">
+      <c r="F51" s="49">
         <v>21202.661315069501</v>
       </c>
-      <c r="G51" s="61">
+      <c r="G51" s="49">
         <v>4841.0219178082098</v>
       </c>
-      <c r="H51" s="61">
+      <c r="H51" s="49">
         <v>2167.59896438136</v>
       </c>
-      <c r="I51" s="61">
+      <c r="I51" s="49">
         <v>142979.54383560701</v>
       </c>
-      <c r="J51" s="61">
+      <c r="J51" s="49">
         <v>164252.25408492901</v>
       </c>
-      <c r="K51" s="61">
+      <c r="K51" s="49">
         <v>46000.398972602103</v>
       </c>
-      <c r="L51" s="61">
+      <c r="L51" s="49">
         <v>10490.511205479999</v>
       </c>
-      <c r="M51" s="61">
+      <c r="M51" s="49">
         <v>390201.04657534102</v>
       </c>
-      <c r="N51" s="61">
+      <c r="N51" s="49">
         <v>6663.7835616430102</v>
       </c>
-      <c r="O51" s="61">
+      <c r="O51" s="49">
         <v>4169.6986301345196</v>
       </c>
-      <c r="P51" s="61">
+      <c r="P51" s="49">
         <v>139007.27544109599</v>
       </c>
-      <c r="Q51" s="61">
+      <c r="Q51" s="49">
         <v>154.78994520520499</v>
       </c>
-      <c r="R51" s="61">
+      <c r="R51" s="49">
         <v>69.655475343287605</v>
       </c>
-      <c r="S51" s="62">
+      <c r="S51" s="50">
         <v>1.8992151045099999E-3</v>
       </c>
-      <c r="T51" s="62">
+      <c r="T51" s="50">
         <v>5.264019836E-5</v>
       </c>
-      <c r="U51" s="62">
+      <c r="U51" s="50">
         <v>7.2231708820000003E-4</v>
       </c>
-      <c r="V51" s="62">
+      <c r="V51" s="50">
         <v>5.5709253999999997E-7</v>
       </c>
-      <c r="W51" s="62">
+      <c r="W51" s="50">
         <v>4.6679888900000002E-6</v>
       </c>
-      <c r="X51" s="62">
+      <c r="X51" s="50">
         <v>1.7158582541500001E-3</v>
       </c>
-      <c r="Y51" s="62">
+      <c r="Y51" s="50">
         <v>5.0842288951999999E-4</v>
       </c>
-      <c r="Z51" s="62">
+      <c r="Z51" s="50">
         <v>4.3801642830000001E-5</v>
       </c>
-      <c r="AA51" s="62">
+      <c r="AA51" s="50">
         <v>1.3559091418000001E-3</v>
       </c>
-      <c r="AB51" s="62">
+      <c r="AB51" s="50">
         <v>1.61601860683E-3</v>
       </c>
-      <c r="AC51" s="62">
+      <c r="AC51" s="50">
         <v>3.1244601129999999E-5</v>
       </c>
-      <c r="AD51" s="62">
+      <c r="AD51" s="50">
         <v>1.440489283E-5</v>
       </c>
-      <c r="AE51" s="62">
+      <c r="AE51" s="50">
         <v>0.18168195221844</v>
       </c>
-      <c r="AF51" s="62">
+      <c r="AF51" s="50">
         <v>8.2952957976220001E-2</v>
       </c>
-      <c r="AG51" s="61">
+      <c r="AG51" s="49">
         <v>139598.705022109</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" s="63" t="s">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A52" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="B52" s="63"/>
-      <c r="C52" s="63" t="s">
+      <c r="B52" s="65"/>
+      <c r="C52" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="D52" s="63"/>
-      <c r="E52" s="63"/>
-      <c r="F52" s="63"/>
-      <c r="G52" s="63"/>
-      <c r="H52" s="63"/>
-      <c r="I52" s="63"/>
-      <c r="J52" s="63"/>
-      <c r="K52" s="63"/>
-      <c r="L52" s="63"/>
-      <c r="M52" s="63"/>
-      <c r="N52" s="63"/>
-      <c r="O52" s="63"/>
-      <c r="P52" s="63"/>
-      <c r="Q52" s="63"/>
-      <c r="R52" s="63"/>
-      <c r="S52" s="63"/>
-      <c r="T52" s="63"/>
-      <c r="U52" s="63"/>
-      <c r="V52" s="63"/>
-      <c r="W52" s="63"/>
-      <c r="X52" s="63"/>
-      <c r="Y52" s="63"/>
-      <c r="Z52" s="63"/>
-      <c r="AA52" s="63"/>
-      <c r="AB52" s="63"/>
-      <c r="AC52" s="63"/>
-      <c r="AD52" s="63"/>
-      <c r="AE52" s="63"/>
-      <c r="AF52" s="63"/>
-      <c r="AG52" s="63"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="65"/>
+      <c r="F52" s="65"/>
+      <c r="G52" s="65"/>
+      <c r="H52" s="65"/>
+      <c r="I52" s="65"/>
+      <c r="J52" s="65"/>
+      <c r="K52" s="65"/>
+      <c r="L52" s="65"/>
+      <c r="M52" s="65"/>
+      <c r="N52" s="65"/>
+      <c r="O52" s="65"/>
+      <c r="P52" s="65"/>
+      <c r="Q52" s="65"/>
+      <c r="R52" s="65"/>
+      <c r="S52" s="65"/>
+      <c r="T52" s="65"/>
+      <c r="U52" s="65"/>
+      <c r="V52" s="65"/>
+      <c r="W52" s="65"/>
+      <c r="X52" s="65"/>
+      <c r="Y52" s="65"/>
+      <c r="Z52" s="65"/>
+      <c r="AA52" s="65"/>
+      <c r="AB52" s="65"/>
+      <c r="AC52" s="65"/>
+      <c r="AD52" s="65"/>
+      <c r="AE52" s="65"/>
+      <c r="AF52" s="65"/>
+      <c r="AG52" s="65"/>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A53" s="63" t="s">
+    <row r="53" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="B53" s="63"/>
-      <c r="C53" s="63" t="s">
+      <c r="B53" s="65"/>
+      <c r="C53" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="D53" s="63"/>
-      <c r="E53" s="63"/>
-      <c r="F53" s="63"/>
-      <c r="G53" s="63"/>
-      <c r="H53" s="63"/>
-      <c r="I53" s="63"/>
-      <c r="J53" s="63"/>
-      <c r="K53" s="63"/>
-      <c r="L53" s="63"/>
-      <c r="M53" s="63"/>
-      <c r="N53" s="63"/>
-      <c r="O53" s="63"/>
-      <c r="P53" s="63"/>
-      <c r="Q53" s="63" t="s">
+      <c r="D53" s="65"/>
+      <c r="E53" s="65"/>
+      <c r="F53" s="65"/>
+      <c r="G53" s="65"/>
+      <c r="H53" s="65"/>
+      <c r="I53" s="65"/>
+      <c r="J53" s="65"/>
+      <c r="K53" s="65"/>
+      <c r="L53" s="65"/>
+      <c r="M53" s="65"/>
+      <c r="N53" s="65"/>
+      <c r="O53" s="65"/>
+      <c r="P53" s="65"/>
+      <c r="Q53" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="R53" s="63"/>
-      <c r="S53" s="63" t="s">
+      <c r="R53" s="65"/>
+      <c r="S53" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="T53" s="63"/>
-      <c r="U53" s="63"/>
-      <c r="V53" s="63"/>
-      <c r="W53" s="63"/>
-      <c r="X53" s="63"/>
-      <c r="Y53" s="63"/>
-      <c r="Z53" s="63"/>
-      <c r="AA53" s="63"/>
-      <c r="AB53" s="63"/>
-      <c r="AC53" s="63"/>
-      <c r="AD53" s="63"/>
-      <c r="AE53" s="63"/>
-      <c r="AF53" s="63"/>
-      <c r="AG53" s="64" t="s">
+      <c r="T53" s="65"/>
+      <c r="U53" s="65"/>
+      <c r="V53" s="65"/>
+      <c r="W53" s="65"/>
+      <c r="X53" s="65"/>
+      <c r="Y53" s="65"/>
+      <c r="Z53" s="65"/>
+      <c r="AA53" s="65"/>
+      <c r="AB53" s="65"/>
+      <c r="AC53" s="65"/>
+      <c r="AD53" s="65"/>
+      <c r="AE53" s="65"/>
+      <c r="AF53" s="65"/>
+      <c r="AG53" s="51" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A54" s="65" t="s">
+    <row r="54" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="B54" s="65" t="s">
+      <c r="B54" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="C54" s="66">
+      <c r="C54" s="53">
         <v>0.47099999999999997</v>
       </c>
-      <c r="D54" s="66">
+      <c r="D54" s="53">
         <v>0.35</v>
       </c>
-      <c r="E54" s="66">
+      <c r="E54" s="53">
         <v>1.4E-2</v>
       </c>
-      <c r="F54" s="66">
+      <c r="F54" s="53">
         <v>0.77</v>
       </c>
-      <c r="G54" s="66">
+      <c r="G54" s="53">
         <v>0.14699999999999999</v>
       </c>
-      <c r="H54" s="66">
+      <c r="H54" s="53">
         <v>0.10100000000000001</v>
       </c>
-      <c r="I54" s="66">
+      <c r="I54" s="53">
         <v>1.369</v>
       </c>
-      <c r="J54" s="66">
+      <c r="J54" s="53">
         <v>2.2269999999999999</v>
       </c>
-      <c r="K54" s="66">
+      <c r="K54" s="53">
         <v>0.65500000000000003</v>
       </c>
-      <c r="L54" s="66">
+      <c r="L54" s="53">
         <v>0.17</v>
       </c>
-      <c r="M54" s="66">
+      <c r="M54" s="53">
         <v>0.82599999999999996</v>
       </c>
-      <c r="N54" s="66">
+      <c r="N54" s="53">
         <v>0.05</v>
       </c>
-      <c r="O54" s="66">
+      <c r="O54" s="53">
         <v>0.11600000000000001</v>
       </c>
-      <c r="P54" s="66">
+      <c r="P54" s="53">
         <v>7.266</v>
       </c>
-      <c r="Q54" s="66"/>
-      <c r="R54" s="66"/>
-      <c r="S54" s="66">
+      <c r="Q54" s="53"/>
+      <c r="R54" s="53"/>
+      <c r="S54" s="53">
         <v>0.11600000000000001</v>
       </c>
-      <c r="T54" s="66">
+      <c r="T54" s="53">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="U54" s="66">
+      <c r="U54" s="53">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="V54" s="66">
+      <c r="V54" s="53">
         <v>1E-3</v>
       </c>
-      <c r="W54" s="66">
+      <c r="W54" s="53">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="X54" s="66">
+      <c r="X54" s="53">
         <v>0.67200000000000004</v>
       </c>
-      <c r="Y54" s="66">
+      <c r="Y54" s="53">
         <v>0.20200000000000001</v>
       </c>
-      <c r="Z54" s="66">
+      <c r="Z54" s="53">
         <v>9.4E-2</v>
       </c>
-      <c r="AA54" s="66">
+      <c r="AA54" s="53">
         <v>0.61899999999999999</v>
       </c>
-      <c r="AB54" s="66">
+      <c r="AB54" s="53">
         <v>0.8</v>
       </c>
-      <c r="AC54" s="66">
+      <c r="AC54" s="53">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="AD54" s="66">
+      <c r="AD54" s="53">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="AE54" s="66"/>
-      <c r="AF54" s="66">
+      <c r="AE54" s="53"/>
+      <c r="AF54" s="53">
         <v>2.5779999999999998</v>
       </c>
-      <c r="AG54" s="66">
+      <c r="AG54" s="53">
         <v>9.8439999999999994</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A55" s="67" t="s">
+    <row r="55" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="67" t="s">
+      <c r="B55" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="C55" s="68">
+      <c r="C55" s="55">
         <v>6.9967741999999999E-2</v>
       </c>
-      <c r="D55" s="68">
+      <c r="D55" s="55">
         <v>5.1451613E-2</v>
       </c>
-      <c r="E55" s="68">
+      <c r="E55" s="55">
         <v>1.774194E-3</v>
       </c>
-      <c r="F55" s="68">
+      <c r="F55" s="55">
         <v>0.11332258100000001</v>
       </c>
-      <c r="G55" s="68">
+      <c r="G55" s="55">
         <v>2.1290323E-2</v>
       </c>
-      <c r="H55" s="68">
+      <c r="H55" s="55">
         <v>1.4193548E-2</v>
       </c>
-      <c r="I55" s="68">
+      <c r="I55" s="55">
         <v>0.202806452</v>
       </c>
-      <c r="J55" s="68">
+      <c r="J55" s="55">
         <v>0.329322581</v>
       </c>
-      <c r="K55" s="68">
+      <c r="K55" s="55">
         <v>9.7354838999999999E-2</v>
       </c>
-      <c r="L55" s="68">
+      <c r="L55" s="55">
         <v>2.483871E-2</v>
       </c>
-      <c r="M55" s="68">
+      <c r="M55" s="55">
         <v>0.122193548</v>
       </c>
-      <c r="N55" s="68">
+      <c r="N55" s="55">
         <v>7.8709680000000008E-3</v>
       </c>
-      <c r="O55" s="68">
+      <c r="O55" s="55">
         <v>1.6741934999999999E-2</v>
       </c>
-      <c r="P55" s="68">
+      <c r="P55" s="55">
         <v>1.0731290339999999</v>
       </c>
-      <c r="Q55" s="68"/>
-      <c r="R55" s="68"/>
-      <c r="S55" s="68">
+      <c r="Q55" s="55"/>
+      <c r="R55" s="55"/>
+      <c r="S55" s="55">
         <v>1.7741935E-2</v>
       </c>
-      <c r="T55" s="68">
+      <c r="T55" s="55">
         <v>3.5483870000000001E-3</v>
       </c>
-      <c r="U55" s="68">
+      <c r="U55" s="55">
         <v>1E-3</v>
       </c>
-      <c r="V55" s="68">
+      <c r="V55" s="55">
         <v>1E-3</v>
       </c>
-      <c r="W55" s="68">
+      <c r="W55" s="55">
         <v>1E-3</v>
       </c>
-      <c r="X55" s="68">
+      <c r="X55" s="55">
         <v>0.106451613</v>
       </c>
-      <c r="Y55" s="68">
+      <c r="Y55" s="55">
         <v>3.1161290000000001E-2</v>
       </c>
-      <c r="Z55" s="68">
+      <c r="Z55" s="55">
         <v>1.4193548E-2</v>
       </c>
-      <c r="AA55" s="68">
+      <c r="AA55" s="55">
         <v>9.2032258000000006E-2</v>
       </c>
-      <c r="AB55" s="68">
+      <c r="AB55" s="55">
         <v>0.118645161</v>
       </c>
-      <c r="AC55" s="68">
+      <c r="AC55" s="55">
         <v>1.774194E-3</v>
       </c>
-      <c r="AD55" s="68">
+      <c r="AD55" s="55">
         <v>4.3225809999999998E-3</v>
       </c>
-      <c r="AE55" s="68"/>
-      <c r="AF55" s="68">
+      <c r="AE55" s="55"/>
+      <c r="AF55" s="55">
         <v>0.39287096700000002</v>
       </c>
-      <c r="AG55" s="68">
+      <c r="AG55" s="55">
         <v>1.4660000010000001</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A56" s="69" t="s">
+    <row r="56" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="69"/>
-      <c r="C56" s="70">
+      <c r="B56" s="56"/>
+      <c r="C56" s="57">
         <v>6.7751594127330006E-2</v>
       </c>
-      <c r="D56" s="70">
+      <c r="D56" s="57">
         <v>6.7517996621179993E-2</v>
       </c>
-      <c r="E56" s="70">
+      <c r="E56" s="57">
         <v>2.5827989629999999E-3</v>
       </c>
-      <c r="F56" s="70">
+      <c r="F56" s="57">
         <v>0.1012096640688</v>
       </c>
-      <c r="G56" s="70">
+      <c r="G56" s="57">
         <v>1.6427794418800001E-2</v>
       </c>
-      <c r="H56" s="70">
+      <c r="H56" s="57">
         <v>1.3252863179000001E-2</v>
       </c>
-      <c r="I56" s="70">
+      <c r="I56" s="57">
         <v>0.27679874573610003</v>
       </c>
-      <c r="J56" s="70">
+      <c r="J56" s="57">
         <v>0.29309487684905999</v>
       </c>
-      <c r="K56" s="70">
+      <c r="K56" s="57">
         <v>9.8226578787400001E-2</v>
       </c>
-      <c r="L56" s="70">
+      <c r="L56" s="57">
         <v>2.441286812738E-2</v>
       </c>
-      <c r="M56" s="70">
+      <c r="M56" s="57">
         <v>6.9921464557099994E-2</v>
       </c>
-      <c r="N56" s="70">
+      <c r="N56" s="57">
         <v>6.6682378854399996E-3</v>
       </c>
-      <c r="O56" s="70">
+      <c r="O56" s="57">
         <v>1.58135694566E-2</v>
       </c>
-      <c r="P56" s="70">
+      <c r="P56" s="57">
         <v>1.05367905277719</v>
       </c>
-      <c r="Q56" s="70">
-        <v>0</v>
-      </c>
-      <c r="R56" s="70">
-        <v>0</v>
-      </c>
-      <c r="S56" s="70">
+      <c r="Q56" s="57">
+        <v>0</v>
+      </c>
+      <c r="R56" s="57">
+        <v>0</v>
+      </c>
+      <c r="S56" s="57">
         <v>2.254991742315E-2</v>
       </c>
-      <c r="T56" s="70">
+      <c r="T56" s="57">
         <v>1.61622E-3</v>
       </c>
-      <c r="U56" s="70">
+      <c r="U56" s="57">
         <v>5.568E-8</v>
       </c>
-      <c r="V56" s="70">
+      <c r="V56" s="57">
         <v>1.2034116E-4</v>
       </c>
-      <c r="W56" s="70">
+      <c r="W56" s="57">
         <v>4.2100200000000002E-4</v>
       </c>
-      <c r="X56" s="70">
+      <c r="X56" s="57">
         <v>9.8097792232000006E-2</v>
       </c>
-      <c r="Y56" s="70">
+      <c r="Y56" s="57">
         <v>2.8658474670999998E-2</v>
       </c>
-      <c r="Z56" s="70">
+      <c r="Z56" s="57">
         <v>1.3436164699999999E-2</v>
       </c>
-      <c r="AA56" s="70">
+      <c r="AA56" s="57">
         <v>9.8725942560000002E-2</v>
       </c>
-      <c r="AB56" s="70">
+      <c r="AB56" s="57">
         <v>0.14012825672000001</v>
       </c>
-      <c r="AC56" s="70">
+      <c r="AC56" s="57">
         <v>1.1872210960000001E-3</v>
       </c>
-      <c r="AD56" s="70">
+      <c r="AD56" s="57">
         <v>1.9998754000000001E-3</v>
       </c>
-      <c r="AE56" s="70">
-        <v>0</v>
-      </c>
-      <c r="AF56" s="70">
+      <c r="AE56" s="57">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="57">
         <v>0.40694126364215</v>
       </c>
-      <c r="AG56" s="70">
+      <c r="AG56" s="57">
         <v>1.4606203164193401</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A57" s="67" t="s">
+    <row r="57" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="67" t="s">
+      <c r="B57" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="C57" s="68">
+      <c r="C57" s="55">
         <v>96.832614846038595</v>
       </c>
-      <c r="D57" s="68">
+      <c r="D57" s="55">
         <v>131.22620008274501</v>
       </c>
-      <c r="E57" s="68">
+      <c r="E57" s="55">
         <v>145.57590449522399</v>
       </c>
-      <c r="F57" s="68">
+      <c r="F57" s="55">
         <v>89.311118027571197</v>
       </c>
-      <c r="G57" s="68">
+      <c r="G57" s="55">
         <v>77.160851053316506</v>
       </c>
-      <c r="H57" s="68">
+      <c r="H57" s="55">
         <v>93.372447671293997</v>
       </c>
-      <c r="I57" s="68">
+      <c r="I57" s="55">
         <v>136.484191211086</v>
       </c>
-      <c r="J57" s="68">
+      <c r="J57" s="55">
         <v>88.999325815759903</v>
       </c>
-      <c r="K57" s="68">
+      <c r="K57" s="55">
         <v>100.895425226269</v>
       </c>
-      <c r="L57" s="68">
+      <c r="L57" s="55">
         <v>98.285571703925001</v>
       </c>
-      <c r="M57" s="68">
+      <c r="M57" s="55">
         <v>57.221895674148001</v>
       </c>
-      <c r="N57" s="68">
+      <c r="N57" s="55">
         <v>84.719412979953603</v>
       </c>
-      <c r="O57" s="68">
+      <c r="O57" s="55">
         <v>94.454849195149706</v>
       </c>
-      <c r="P57" s="68">
+      <c r="P57" s="55">
         <v>98.187544963692602</v>
       </c>
-      <c r="Q57" s="68"/>
-      <c r="R57" s="68"/>
-      <c r="S57" s="68">
+      <c r="Q57" s="55"/>
+      <c r="R57" s="55"/>
+      <c r="S57" s="55">
         <v>127.099538033196</v>
       </c>
-      <c r="T57" s="68">
+      <c r="T57" s="55">
         <v>45.548019424036802</v>
       </c>
-      <c r="U57" s="68">
+      <c r="U57" s="55">
         <v>5.568E-3</v>
       </c>
-      <c r="V57" s="68">
+      <c r="V57" s="55">
         <v>12.034115999999999</v>
       </c>
-      <c r="W57" s="68">
+      <c r="W57" s="55">
         <v>42.100200000000001</v>
       </c>
-      <c r="X57" s="68">
+      <c r="X57" s="55">
         <v>92.152471406891607</v>
       </c>
-      <c r="Y57" s="68">
+      <c r="Y57" s="55">
         <v>91.968190890043303</v>
       </c>
-      <c r="Z57" s="68">
+      <c r="Z57" s="55">
         <v>94.663890240833297</v>
       </c>
-      <c r="AA57" s="68">
+      <c r="AA57" s="55">
         <v>107.273193883822</v>
       </c>
-      <c r="AB57" s="68">
+      <c r="AB57" s="55">
         <v>118.10701383767299</v>
       </c>
-      <c r="AC57" s="68">
+      <c r="AC57" s="55">
         <v>66.916081104997502</v>
       </c>
-      <c r="AD57" s="68">
+      <c r="AD57" s="55">
         <v>46.265770381168103</v>
       </c>
-      <c r="AE57" s="68"/>
-      <c r="AF57" s="68">
+      <c r="AE57" s="55"/>
+      <c r="AF57" s="55">
         <v>103.581404029315</v>
       </c>
-      <c r="AG57" s="68">
+      <c r="AG57" s="55">
         <v>99.6330365227155</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A58" s="60" t="s">
+    <row r="58" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="60" t="s">
+      <c r="B58" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="C58" s="62">
+      <c r="C58" s="50">
         <v>14.3846272032547</v>
       </c>
-      <c r="D58" s="62">
+      <c r="D58" s="50">
         <v>19.290856177479998</v>
       </c>
-      <c r="E58" s="62">
+      <c r="E58" s="50">
         <v>18.448564021428499</v>
       </c>
-      <c r="F58" s="62">
+      <c r="F58" s="50">
         <v>13.1441122167272</v>
       </c>
-      <c r="G58" s="62">
+      <c r="G58" s="50">
         <v>11.1753703529251</v>
       </c>
-      <c r="H58" s="62">
+      <c r="H58" s="50">
         <v>13.1216467118811</v>
       </c>
-      <c r="I58" s="62">
+      <c r="I58" s="50">
         <v>20.219046437991199</v>
       </c>
-      <c r="J58" s="62">
+      <c r="J58" s="50">
         <v>13.1609733654719</v>
       </c>
-      <c r="K58" s="62">
+      <c r="K58" s="50">
         <v>14.9964242423511</v>
       </c>
-      <c r="L58" s="62">
+      <c r="L58" s="50">
         <v>14.3605106631647</v>
       </c>
-      <c r="M58" s="62">
+      <c r="M58" s="50">
         <v>8.4650683483171907</v>
       </c>
-      <c r="N58" s="62">
+      <c r="N58" s="50">
         <v>13.33647577088</v>
       </c>
-      <c r="O58" s="62">
+      <c r="O58" s="50">
         <v>13.6323874625862</v>
       </c>
-      <c r="P58" s="62">
+      <c r="P58" s="50">
         <v>14.5015008639855</v>
       </c>
-      <c r="Q58" s="62"/>
-      <c r="R58" s="62"/>
-      <c r="S58" s="62">
+      <c r="Q58" s="50"/>
+      <c r="R58" s="50"/>
+      <c r="S58" s="50">
         <v>19.439583985474101</v>
       </c>
-      <c r="T58" s="62">
+      <c r="T58" s="50">
         <v>6.46488</v>
       </c>
-      <c r="U58" s="62">
+      <c r="U58" s="50">
         <v>1.392E-3</v>
       </c>
-      <c r="V58" s="62">
+      <c r="V58" s="50">
         <v>12.034115999999999</v>
       </c>
-      <c r="W58" s="62">
+      <c r="W58" s="50">
         <v>10.52505</v>
       </c>
-      <c r="X58" s="62">
+      <c r="X58" s="50">
         <v>14.5978857488095</v>
       </c>
-      <c r="Y58" s="62">
+      <c r="Y58" s="50">
         <v>14.187363698514799</v>
       </c>
-      <c r="Z58" s="62">
+      <c r="Z58" s="50">
         <v>14.293792234042501</v>
       </c>
-      <c r="AA58" s="62">
+      <c r="AA58" s="50">
         <v>15.9492637415185</v>
       </c>
-      <c r="AB58" s="62">
+      <c r="AB58" s="50">
         <v>17.516032089999999</v>
       </c>
-      <c r="AC58" s="62">
+      <c r="AC58" s="50">
         <v>13.1913455111111</v>
       </c>
-      <c r="AD58" s="62">
+      <c r="AD58" s="50">
         <v>6.2496106249999999</v>
       </c>
-      <c r="AE58" s="62"/>
-      <c r="AF58" s="62">
+      <c r="AE58" s="50"/>
+      <c r="AF58" s="50">
         <v>15.785153748725699</v>
       </c>
-      <c r="AG58" s="62">
+      <c r="AG58" s="50">
         <v>14.837670829127701</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A59" s="71" t="s">
+    <row r="59" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A59" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="B59" s="72" t="s">
+      <c r="B59" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="C59" s="73">
+      <c r="C59" s="59">
         <v>0.50574823530049995</v>
       </c>
-      <c r="D59" s="73">
+      <c r="D59" s="59">
         <v>0.45265177836129999</v>
       </c>
-      <c r="E59" s="73">
-        <v>0</v>
-      </c>
-      <c r="F59" s="73">
+      <c r="E59" s="59">
+        <v>0</v>
+      </c>
+      <c r="F59" s="59">
         <v>0.44315559400479998</v>
       </c>
-      <c r="G59" s="73">
+      <c r="G59" s="59">
         <v>0.21914233301790001</v>
       </c>
-      <c r="H59" s="73">
+      <c r="H59" s="59">
         <v>0.18657599999819999</v>
       </c>
-      <c r="I59" s="73">
+      <c r="I59" s="59">
         <v>2.18556351828</v>
       </c>
-      <c r="J59" s="73">
+      <c r="J59" s="59">
         <v>2.6806080600006998</v>
       </c>
-      <c r="K59" s="73">
+      <c r="K59" s="59">
         <v>0.27796587775429998</v>
       </c>
-      <c r="L59" s="73">
+      <c r="L59" s="59">
         <v>2.1216535837600001E-2</v>
       </c>
-      <c r="M59" s="73">
+      <c r="M59" s="59">
         <v>0.7276961999996</v>
       </c>
-      <c r="N59" s="73">
+      <c r="N59" s="59">
         <v>5.9716879419600001E-2</v>
       </c>
-      <c r="O59" s="73">
+      <c r="O59" s="59">
         <v>5.25066799998E-2</v>
       </c>
-      <c r="P59" s="73">
+      <c r="P59" s="59">
         <v>7.8125476919743004</v>
       </c>
-      <c r="Q59" s="73">
+      <c r="Q59" s="59">
         <v>7.2553500005999999E-3</v>
       </c>
-      <c r="R59" s="73">
+      <c r="R59" s="59">
         <v>7.2553500005999999E-3</v>
       </c>
-      <c r="S59" s="73">
+      <c r="S59" s="59">
         <v>9.9531064099999997E-2</v>
       </c>
-      <c r="T59" s="73">
+      <c r="T59" s="59">
         <v>3.11744724E-2</v>
       </c>
-      <c r="U59" s="73">
-        <v>0</v>
-      </c>
-      <c r="V59" s="73">
+      <c r="U59" s="59">
+        <v>0</v>
+      </c>
+      <c r="V59" s="59">
         <v>9.4640429999999997E-4</v>
       </c>
-      <c r="W59" s="73">
+      <c r="W59" s="59">
         <v>6.9834336E-3</v>
       </c>
-      <c r="X59" s="73">
+      <c r="X59" s="59">
         <v>0.61933886637400004</v>
       </c>
-      <c r="Y59" s="73">
+      <c r="Y59" s="59">
         <v>0.27731972387800002</v>
       </c>
-      <c r="Z59" s="73">
+      <c r="Z59" s="59">
         <v>0.1002750027</v>
       </c>
-      <c r="AA59" s="73">
+      <c r="AA59" s="59">
         <v>0.70981551440000001</v>
       </c>
-      <c r="AB59" s="73">
+      <c r="AB59" s="59">
         <v>1.4684396805</v>
       </c>
-      <c r="AC59" s="73">
+      <c r="AC59" s="59">
         <v>4.8819468000000001E-3</v>
       </c>
-      <c r="AD59" s="73">
+      <c r="AD59" s="59">
         <v>8.5768153999999999E-3</v>
       </c>
-      <c r="AE59" s="73">
+      <c r="AE59" s="59">
         <v>0.53936415029999996</v>
       </c>
-      <c r="AF59" s="73">
+      <c r="AF59" s="59">
         <v>3.8666470747520001</v>
       </c>
-      <c r="AG59" s="73">
+      <c r="AG59" s="59">
         <v>11.686450116726901</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A60" s="71"/>
-      <c r="B60" s="72" t="s">
+    <row r="60" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="66"/>
+      <c r="B60" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="C60" s="73">
+      <c r="C60" s="59">
         <v>0.45862536142479998</v>
       </c>
-      <c r="D60" s="73">
+      <c r="D60" s="59">
         <v>0.34662770991050001</v>
       </c>
-      <c r="E60" s="73">
-        <v>0</v>
-      </c>
-      <c r="F60" s="73">
+      <c r="E60" s="59">
+        <v>0</v>
+      </c>
+      <c r="F60" s="59">
         <v>0.65409551200600002</v>
       </c>
-      <c r="G60" s="73">
+      <c r="G60" s="59">
         <v>7.7207052510299995E-2</v>
       </c>
-      <c r="H60" s="73">
+      <c r="H60" s="59">
         <v>0.1691660000039</v>
       </c>
-      <c r="I60" s="73">
+      <c r="I60" s="59">
         <v>0.16111269283900001</v>
       </c>
-      <c r="J60" s="73">
+      <c r="J60" s="59">
         <v>2.4631687600003001</v>
       </c>
-      <c r="K60" s="73">
+      <c r="K60" s="59">
         <v>0.2437548475047</v>
       </c>
-      <c r="L60" s="73">
+      <c r="L60" s="59">
         <v>5.7699969975000001E-2</v>
       </c>
-      <c r="M60" s="73">
+      <c r="M60" s="59">
         <v>1.1035464041530001</v>
       </c>
-      <c r="N60" s="73">
+      <c r="N60" s="59">
         <v>5.7970123530500003E-2</v>
       </c>
-      <c r="O60" s="73">
+      <c r="O60" s="59">
         <v>5.2864919999899999E-2</v>
       </c>
-      <c r="P60" s="73">
+      <c r="P60" s="59">
         <v>5.8458393538579001</v>
       </c>
-      <c r="Q60" s="73">
+      <c r="Q60" s="59">
         <v>5.2960500004000004E-3</v>
       </c>
-      <c r="R60" s="73">
+      <c r="R60" s="59">
         <v>5.2960500004000004E-3</v>
       </c>
-      <c r="S60" s="73">
+      <c r="S60" s="59">
         <v>7.9138956499999996E-2</v>
       </c>
-      <c r="T60" s="73">
+      <c r="T60" s="59">
         <v>2.1863520300000001E-2</v>
       </c>
-      <c r="U60" s="73">
-        <v>0</v>
-      </c>
-      <c r="V60" s="73">
+      <c r="U60" s="59">
+        <v>0</v>
+      </c>
+      <c r="V60" s="59">
         <v>1.6170035000000001E-3</v>
       </c>
-      <c r="W60" s="73">
+      <c r="W60" s="59">
         <v>2.3245111000000001E-3</v>
       </c>
-      <c r="X60" s="73">
+      <c r="X60" s="59">
         <v>0.7185337222</v>
       </c>
-      <c r="Y60" s="73">
+      <c r="Y60" s="59">
         <v>0.2330015953</v>
       </c>
-      <c r="Z60" s="73">
+      <c r="Z60" s="59">
         <v>0.117705005</v>
       </c>
-      <c r="AA60" s="73">
+      <c r="AA60" s="59">
         <v>0.61024679800000003</v>
       </c>
-      <c r="AB60" s="73">
+      <c r="AB60" s="59">
         <v>1.1435139132000001</v>
       </c>
-      <c r="AC60" s="73">
+      <c r="AC60" s="59">
         <v>6.6903683999999996E-3</v>
       </c>
-      <c r="AD60" s="73">
+      <c r="AD60" s="59">
         <v>8.1769977000000008E-3</v>
       </c>
-      <c r="AE60" s="73">
+      <c r="AE60" s="59">
         <v>0.68836905120000003</v>
       </c>
-      <c r="AF60" s="73">
+      <c r="AF60" s="59">
         <v>3.6311814424</v>
       </c>
-      <c r="AG60" s="73">
+      <c r="AG60" s="59">
         <v>9.4823168462582998</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A61" s="71"/>
-      <c r="B61" s="72" t="s">
+    <row r="61" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A61" s="66"/>
+      <c r="B61" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="C61" s="73">
+      <c r="C61" s="59">
         <v>0.4</v>
       </c>
-      <c r="D61" s="73">
+      <c r="D61" s="59">
         <v>0.39</v>
       </c>
-      <c r="E61" s="73">
-        <v>0</v>
-      </c>
-      <c r="F61" s="73">
+      <c r="E61" s="59">
+        <v>0</v>
+      </c>
+      <c r="F61" s="59">
         <v>0.66012030675699995</v>
       </c>
-      <c r="G61" s="73">
+      <c r="G61" s="59">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="H61" s="73">
+      <c r="H61" s="59">
         <v>0.124</v>
       </c>
-      <c r="I61" s="73">
+      <c r="I61" s="59">
         <v>1.6839999999999999</v>
       </c>
-      <c r="J61" s="73">
+      <c r="J61" s="59">
         <v>2.3170000000000002</v>
       </c>
-      <c r="K61" s="73">
+      <c r="K61" s="59">
         <v>0.58299999999999996</v>
       </c>
-      <c r="L61" s="73">
+      <c r="L61" s="59">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="M61" s="73">
+      <c r="M61" s="59">
         <v>0.72399999999999998</v>
       </c>
-      <c r="N61" s="73">
+      <c r="N61" s="59">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="O61" s="73">
+      <c r="O61" s="59">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="P61" s="73">
+      <c r="P61" s="59">
         <v>7.175120306757</v>
       </c>
-      <c r="Q61" s="73">
+      <c r="Q61" s="59">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="R61" s="73">
+      <c r="R61" s="59">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="S61" s="73">
+      <c r="S61" s="59">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="T61" s="73">
+      <c r="T61" s="59">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="U61" s="73">
-        <v>0</v>
-      </c>
-      <c r="V61" s="73">
+      <c r="U61" s="59">
+        <v>0</v>
+      </c>
+      <c r="V61" s="59">
         <v>1E-3</v>
       </c>
-      <c r="W61" s="73">
+      <c r="W61" s="59">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="X61" s="73">
+      <c r="X61" s="59">
         <v>0.65500000000000003</v>
       </c>
-      <c r="Y61" s="73">
+      <c r="Y61" s="59">
         <v>0.17799999999999999</v>
       </c>
-      <c r="Z61" s="73">
+      <c r="Z61" s="59">
         <v>0.114</v>
       </c>
-      <c r="AA61" s="73">
+      <c r="AA61" s="59">
         <v>0.70099999999999996</v>
       </c>
-      <c r="AB61" s="73">
+      <c r="AB61" s="59">
         <v>1.1379999999999999</v>
       </c>
-      <c r="AC61" s="73">
+      <c r="AC61" s="59">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="AD61" s="73">
+      <c r="AD61" s="59">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="AE61" s="73">
+      <c r="AE61" s="59">
         <v>0.41799999999999998</v>
       </c>
-      <c r="AF61" s="73">
+      <c r="AF61" s="59">
         <v>3.34</v>
       </c>
-      <c r="AG61" s="73">
+      <c r="AG61" s="59">
         <v>10.518120306757</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A62" s="71"/>
-      <c r="B62" s="72" t="s">
+    <row r="62" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A62" s="66"/>
+      <c r="B62" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="C62" s="73">
+      <c r="C62" s="59">
         <v>0.48699999999999999</v>
       </c>
-      <c r="D62" s="73">
+      <c r="D62" s="59">
         <v>0.36599999999999999</v>
       </c>
-      <c r="E62" s="73">
-        <v>0</v>
-      </c>
-      <c r="F62" s="73">
+      <c r="E62" s="59">
+        <v>0</v>
+      </c>
+      <c r="F62" s="59">
         <v>0.82799999999999996</v>
       </c>
-      <c r="G62" s="73">
+      <c r="G62" s="59">
         <v>0.112</v>
       </c>
-      <c r="H62" s="73">
+      <c r="H62" s="59">
         <v>0.105</v>
       </c>
-      <c r="I62" s="73">
+      <c r="I62" s="59">
         <v>1.4830000000000001</v>
       </c>
-      <c r="J62" s="73">
+      <c r="J62" s="59">
         <v>2.2040000000000002</v>
       </c>
-      <c r="K62" s="73">
+      <c r="K62" s="59">
         <v>0.63</v>
       </c>
-      <c r="L62" s="73">
+      <c r="L62" s="59">
         <v>0.14699999999999999</v>
       </c>
-      <c r="M62" s="73">
+      <c r="M62" s="59">
         <v>0.76</v>
       </c>
-      <c r="N62" s="73">
+      <c r="N62" s="59">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="O62" s="73">
+      <c r="O62" s="59">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="P62" s="73">
+      <c r="P62" s="59">
         <v>7.2629999999999999</v>
       </c>
-      <c r="Q62" s="73">
+      <c r="Q62" s="59">
         <v>2E-3</v>
       </c>
-      <c r="R62" s="73">
+      <c r="R62" s="59">
         <v>2E-3</v>
       </c>
-      <c r="S62" s="73">
+      <c r="S62" s="59">
         <v>0.11600000000000001</v>
       </c>
-      <c r="T62" s="73">
+      <c r="T62" s="59">
         <v>2.7E-2</v>
       </c>
-      <c r="U62" s="73">
-        <v>0</v>
-      </c>
-      <c r="V62" s="73">
+      <c r="U62" s="59">
+        <v>0</v>
+      </c>
+      <c r="V62" s="59">
         <v>1E-3</v>
       </c>
-      <c r="W62" s="73">
+      <c r="W62" s="59">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="X62" s="73">
+      <c r="X62" s="59">
         <v>0.65700000000000003</v>
       </c>
-      <c r="Y62" s="73">
+      <c r="Y62" s="59">
         <v>0.19500000000000001</v>
       </c>
-      <c r="Z62" s="73">
+      <c r="Z62" s="59">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="AA62" s="73">
+      <c r="AA62" s="59">
         <v>0.70299999999999996</v>
       </c>
-      <c r="AB62" s="73">
+      <c r="AB62" s="59">
         <v>1.032</v>
       </c>
-      <c r="AC62" s="73">
+      <c r="AC62" s="59">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="AD62" s="73">
+      <c r="AD62" s="59">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="AE62" s="73">
+      <c r="AE62" s="59">
         <v>0.159</v>
       </c>
-      <c r="AF62" s="73">
+      <c r="AF62" s="59">
         <v>3.0129999999999999</v>
       </c>
-      <c r="AG62" s="73">
+      <c r="AG62" s="59">
         <v>10.278</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A63" s="71"/>
-      <c r="B63" s="72" t="s">
+    <row r="63" spans="1:33" ht="16" x14ac:dyDescent="0.2">
+      <c r="A63" s="66"/>
+      <c r="B63" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="C63" s="73">
+      <c r="C63" s="59">
         <v>0.47199999999999998</v>
       </c>
-      <c r="D63" s="73">
+      <c r="D63" s="59">
         <v>0.35399999999999998</v>
       </c>
-      <c r="E63" s="73">
+      <c r="E63" s="59">
         <v>8.5268952798000005E-3</v>
       </c>
-      <c r="F63" s="73">
+      <c r="F63" s="59">
         <v>0.73399999999999999</v>
       </c>
-      <c r="G63" s="73">
+      <c r="G63" s="59">
         <v>0.13</v>
       </c>
-      <c r="H63" s="73">
+      <c r="H63" s="59">
         <v>0.10299999999999999</v>
       </c>
-      <c r="I63" s="73">
+      <c r="I63" s="59">
         <v>1.4159999999999999</v>
       </c>
-      <c r="J63" s="73">
+      <c r="J63" s="59">
         <v>2.0950000000000002</v>
       </c>
-      <c r="K63" s="73">
+      <c r="K63" s="59">
         <v>0.57499999999999996</v>
       </c>
-      <c r="L63" s="73">
+      <c r="L63" s="59">
         <v>0.13600000000000001</v>
       </c>
-      <c r="M63" s="73">
+      <c r="M63" s="59">
         <v>0.748</v>
       </c>
-      <c r="N63" s="73">
+      <c r="N63" s="59">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="O63" s="73">
+      <c r="O63" s="59">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="P63" s="73">
+      <c r="P63" s="59">
         <v>6.9075268952798003</v>
       </c>
-      <c r="Q63" s="73">
+      <c r="Q63" s="59">
         <v>5.9878491460000002E-3</v>
       </c>
-      <c r="R63" s="73">
+      <c r="R63" s="59">
         <v>5.9878491460000002E-3</v>
       </c>
-      <c r="S63" s="73">
+      <c r="S63" s="59">
         <v>0.127</v>
       </c>
-      <c r="T63" s="73">
+      <c r="T63" s="59">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="U63" s="73">
+      <c r="U63" s="59">
         <v>1.5947786E-3</v>
       </c>
-      <c r="V63" s="73">
+      <c r="V63" s="59">
         <v>1E-3</v>
       </c>
-      <c r="W63" s="73">
+      <c r="W63" s="59">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="X63" s="73">
+      <c r="X63" s="59">
         <v>0.67200000000000004</v>
       </c>
-      <c r="Y63" s="73">
+      <c r="Y63" s="59">
         <v>0.19600000000000001</v>
       </c>
-      <c r="Z63" s="73">
+      <c r="Z63" s="59">
         <v>0.10100000000000001</v>
       </c>
-      <c r="AA63" s="73">
+      <c r="AA63" s="59">
         <v>0.623</v>
       </c>
-      <c r="AB63" s="73">
+      <c r="AB63" s="59">
         <v>0.96499999999999997</v>
       </c>
-      <c r="AC63" s="73">
+      <c r="AC63" s="59">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="AD63" s="73">
+      <c r="AD63" s="59">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="AE63" s="73">
+      <c r="AE63" s="59">
         <v>4.6838600000000001E-2</v>
       </c>
-      <c r="AF63" s="73">
+      <c r="AF63" s="59">
         <v>2.7924333786000002</v>
       </c>
-      <c r="AG63" s="73">
+      <c r="AG63" s="59">
         <v>9.7059481230258005</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+    <row r="65" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+    <row r="66" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="67"/>
+      <c r="H66" s="67"/>
+      <c r="I66" s="67"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="8"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A68" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="8"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="8"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="8"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="8"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="8"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="8"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="6"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
+      <c r="B76" s="64"/>
+      <c r="C76" s="64"/>
+      <c r="D76" s="64"/>
+      <c r="E76" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="C10:O10"/>
+    <mergeCell ref="S10:AE10"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C5:O5"/>
+    <mergeCell ref="S5:AE5"/>
+    <mergeCell ref="C9:O9"/>
+    <mergeCell ref="S9:AE9"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C52:AG52"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="C53:P53"/>
@@ -7928,58 +7992,6 @@
     <mergeCell ref="S53:AF53"/>
     <mergeCell ref="A59:A63"/>
     <mergeCell ref="C66:I66"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="C52:AG52"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="C5:O5"/>
-    <mergeCell ref="S5:AE5"/>
-    <mergeCell ref="C9:O9"/>
-    <mergeCell ref="S9:AE9"/>
-    <mergeCell ref="C10:O10"/>
-    <mergeCell ref="S10:AE10"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="29" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7990,12 +8002,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18293585-FC0C-40C8-9EA5-CF2A33ED63E4}">
   <dimension ref="B2:BD4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:56" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:56" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>73</v>
       </c>
@@ -8162,7 +8174,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="2:56" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:56" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>60</v>
       </c>
@@ -8329,7 +8341,7 @@
         <v>144689.63570499999</v>
       </c>
     </row>
-    <row r="4" spans="2:56" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:56" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>127</v>
       </c>
@@ -8506,126 +8518,237 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A45:G49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A45:G56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="7" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="7" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="45" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+    <row r="45" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A45" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="77" t="s">
         <v>129</v>
       </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10" t="s">
+      <c r="C45" s="77"/>
+      <c r="D45" s="77" t="s">
         <v>130</v>
       </c>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10" t="s">
+      <c r="E45" s="77"/>
+      <c r="F45" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="G45" s="10"/>
+      <c r="G45" s="77"/>
     </row>
-    <row r="46" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11" t="s">
+    <row r="46" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A46" s="77"/>
+      <c r="B46" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G46" s="11" t="s">
+      <c r="G46" s="7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="75" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="80" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="76">
+      <c r="B47" s="81">
         <v>142607.96199790001</v>
       </c>
-      <c r="C47" s="76">
+      <c r="C47" s="81">
         <v>142607.96199790001</v>
       </c>
-      <c r="D47" s="76">
+      <c r="D47" s="81">
         <v>3.3404324000000001</v>
       </c>
-      <c r="E47" s="76">
+      <c r="E47" s="81">
         <v>3.3404324000000001</v>
       </c>
-      <c r="F47" s="76">
+      <c r="F47" s="81">
         <v>163619.2818539</v>
       </c>
-      <c r="G47" s="76">
+      <c r="G47" s="81">
         <v>163619.2818539</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="77" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="80" t="s">
         <v>127</v>
       </c>
-      <c r="B48" s="74">
+      <c r="B48" s="81">
         <v>146458.0410959</v>
       </c>
-      <c r="C48" s="74">
+      <c r="C48" s="81">
         <v>146216.43988739999</v>
       </c>
-      <c r="D48" s="74">
+      <c r="D48" s="81">
         <v>7.0630137</v>
       </c>
-      <c r="E48" s="74">
+      <c r="E48" s="81">
         <v>7.2753883000000004</v>
       </c>
-      <c r="F48" s="74">
+      <c r="F48" s="81">
         <v>190884.3972603</v>
       </c>
-      <c r="G48" s="74">
+      <c r="G48" s="81">
         <v>191978.6321546</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="12">
+      <c r="B49" s="81">
         <v>97.371206750280706</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="81">
         <v>97.532098379444307</v>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" s="81">
         <v>47.294717834116597</v>
       </c>
-      <c r="E49" s="12">
+      <c r="E49" s="81">
         <v>45.914145915758198</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F49" s="81">
         <v>85.716425335057707</v>
       </c>
-      <c r="G49" s="12">
+      <c r="G49" s="81">
         <v>85.2278610476491</v>
       </c>
+    </row>
+    <row r="52" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A52" s="77" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" s="77" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" s="77"/>
+      <c r="D52" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="E52" s="77"/>
+      <c r="F52" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="G52" s="77"/>
+    </row>
+    <row r="53" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A53" s="77"/>
+      <c r="B53" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="61" t="s">
+        <v>134</v>
+      </c>
+      <c r="B54" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!P48</f>
+        <v>142607.96199787699</v>
+      </c>
+      <c r="C54" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!P48</f>
+        <v>142607.96199787699</v>
+      </c>
+      <c r="D54" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!AF48</f>
+        <v>3.3404324095481499</v>
+      </c>
+      <c r="E54" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!AF48</f>
+        <v>3.3404324095481499</v>
+      </c>
+      <c r="F54" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!AG48</f>
+        <v>163619.28185393501</v>
+      </c>
+      <c r="G54" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!AG48</f>
+        <v>163619.28185393501</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!P46</f>
+        <v>146458.04109588999</v>
+      </c>
+      <c r="C55" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!P47</f>
+        <v>146216.439887407</v>
+      </c>
+      <c r="D55" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!AF46</f>
+        <v>7.0630136986301402</v>
+      </c>
+      <c r="E55" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!AF47</f>
+        <v>7.2753882777777799</v>
+      </c>
+      <c r="F55" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!AG46</f>
+        <v>190884.39726027299</v>
+      </c>
+      <c r="G55" s="78">
+        <f>'DPR ( 25-MAY-2026 )'!AG47</f>
+        <v>191978.63215462901</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="F45:G45"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="47" fitToHeight="0" orientation="landscape" r:id="rId1"/>
